--- a/docs/data/jp/xlsx/4490.xlsx
+++ b/docs/data/jp/xlsx/4490.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -756,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC195"/>
+  <dimension ref="A1:AC201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4244,11 +4247,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5485,7 +5488,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5737,582 +5740,676 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>임원 보수</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="n">
-        <v>23.271</v>
-      </c>
-      <c r="D79" s="22" t="n">
-        <v>17.901</v>
-      </c>
-      <c r="E79" s="22" t="n">
-        <v>16.036</v>
-      </c>
-      <c r="F79" s="22" t="n">
-        <v>8.597</v>
-      </c>
-      <c r="G79" s="22" t="n">
-        <v>7.241</v>
-      </c>
-      <c r="H79" s="22" t="n">
-        <v>7.247</v>
-      </c>
-      <c r="I79" s="22" t="n">
-        <v>7.247</v>
-      </c>
-      <c r="J79" s="22" t="n">
-        <v>16.602</v>
-      </c>
-      <c r="K79" s="22" t="n">
-        <v>16.603</v>
-      </c>
-      <c r="L79" s="22" t="n">
-        <v>16.602</v>
-      </c>
-      <c r="M79" s="22" t="n">
-        <v>16.602</v>
-      </c>
-      <c r="N79" s="22" t="n">
-        <v>16.954</v>
-      </c>
-      <c r="T79" s="22" t="n">
-        <v>24.857</v>
-      </c>
-      <c r="U79" s="22" t="n">
-        <v>55.675</v>
-      </c>
-      <c r="V79" s="22" t="n">
-        <v>17.901</v>
-      </c>
-      <c r="W79" s="22" t="n">
-        <v>7.247</v>
-      </c>
-      <c r="X79" s="22" t="n">
-        <v>16.602</v>
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>급여·수당</t>
+          <t>임원 보수</t>
         </is>
       </c>
       <c r="C80" s="22" t="n">
-        <v>988.177</v>
+        <v>23.271</v>
       </c>
       <c r="D80" s="22" t="n">
-        <v>971.083</v>
+        <v>17.901</v>
       </c>
       <c r="E80" s="22" t="n">
-        <v>1000.735</v>
+        <v>16.036</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>1066.51</v>
+        <v>8.597</v>
       </c>
       <c r="G80" s="22" t="n">
-        <v>1018.407</v>
+        <v>7.241</v>
       </c>
       <c r="H80" s="22" t="n">
-        <v>1055.527</v>
+        <v>7.247</v>
       </c>
       <c r="I80" s="22" t="n">
-        <v>1029.786</v>
+        <v>7.247</v>
       </c>
       <c r="J80" s="22" t="n">
-        <v>1004.856</v>
+        <v>16.602</v>
       </c>
       <c r="K80" s="22" t="n">
-        <v>1023.183</v>
+        <v>16.603</v>
       </c>
       <c r="L80" s="22" t="n">
-        <v>1038.727</v>
+        <v>16.602</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>1083.964</v>
+        <v>16.602</v>
       </c>
       <c r="N80" s="22" t="n">
-        <v>1116.816</v>
+        <v>16.954</v>
       </c>
       <c r="T80" s="22" t="n">
-        <v>642.314</v>
+        <v>24.857</v>
       </c>
       <c r="U80" s="22" t="n">
-        <v>905.285</v>
+        <v>55.675</v>
       </c>
       <c r="V80" s="22" t="n">
-        <v>971.083</v>
+        <v>17.901</v>
       </c>
       <c r="W80" s="22" t="n">
-        <v>1055.527</v>
+        <v>7.247</v>
       </c>
       <c r="X80" s="22" t="n">
-        <v>1038.727</v>
+        <v>16.602</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 전입</t>
+          <t>급여·수당</t>
         </is>
       </c>
       <c r="C81" s="22" t="n">
-        <v>-7.676</v>
+        <v>988.177</v>
       </c>
       <c r="D81" s="22" t="n">
-        <v>208.356</v>
+        <v>971.083</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>176.872</v>
+        <v>1000.735</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>173.959</v>
+        <v>1066.51</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>149.688</v>
+        <v>1018.407</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>17.939</v>
+        <v>1055.527</v>
       </c>
       <c r="I81" s="22" t="n">
-        <v>156.451</v>
+        <v>1029.786</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>130.552</v>
+        <v>1004.856</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>144.566</v>
+        <v>1023.183</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>57.646</v>
+        <v>1038.727</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>177.754</v>
+        <v>1083.964</v>
       </c>
       <c r="N81" s="22" t="n">
-        <v>171.448</v>
+        <v>1116.816</v>
       </c>
       <c r="T81" s="22" t="n">
-        <v>55.676</v>
+        <v>642.314</v>
       </c>
       <c r="U81" s="22" t="n">
-        <v>-11.157</v>
+        <v>905.285</v>
       </c>
       <c r="V81" s="22" t="n">
-        <v>208.356</v>
+        <v>971.083</v>
       </c>
       <c r="W81" s="22" t="n">
-        <v>17.939</v>
+        <v>1055.527</v>
       </c>
       <c r="X81" s="22" t="n">
-        <v>57.646</v>
+        <v>1038.727</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>지급보수</t>
+          <t>상여충당금 전입</t>
         </is>
       </c>
       <c r="C82" s="22" t="n">
-        <v>260.467</v>
+        <v>-7.676</v>
       </c>
       <c r="D82" s="22" t="n">
-        <v>-61.5</v>
+        <v>208.356</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>106.426</v>
+        <v>176.872</v>
       </c>
       <c r="F82" s="22" t="n">
-        <v>113.369</v>
+        <v>173.959</v>
       </c>
       <c r="G82" s="22" t="n">
-        <v>84.58199999999999</v>
+        <v>149.688</v>
       </c>
       <c r="H82" s="22" t="n">
-        <v>109.174</v>
+        <v>17.939</v>
       </c>
       <c r="I82" s="22" t="n">
-        <v>87.303</v>
+        <v>156.451</v>
       </c>
       <c r="J82" s="22" t="n">
-        <v>98.54300000000001</v>
+        <v>130.552</v>
       </c>
       <c r="K82" s="22" t="n">
-        <v>81.78400000000001</v>
+        <v>144.566</v>
       </c>
       <c r="L82" s="22" t="n">
-        <v>110.14</v>
+        <v>57.646</v>
       </c>
       <c r="M82" s="22" t="n">
-        <v>86.58</v>
+        <v>177.754</v>
       </c>
       <c r="N82" s="22" t="n">
-        <v>123.017</v>
+        <v>171.448</v>
       </c>
       <c r="T82" s="22" t="n">
-        <v>112.725</v>
+        <v>55.676</v>
       </c>
       <c r="U82" s="22" t="n">
-        <v>157.443</v>
+        <v>-11.157</v>
       </c>
       <c r="V82" s="22" t="n">
-        <v>-61.5</v>
+        <v>208.356</v>
       </c>
       <c r="W82" s="22" t="n">
-        <v>109.174</v>
+        <v>17.939</v>
       </c>
       <c r="X82" s="22" t="n">
-        <v>110.14</v>
+        <v>57.646</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>지급보수</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>1078.22</v>
+        <v>260.467</v>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>-61.5</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>835.3150000000001</v>
+        <v>106.426</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>855.228</v>
+        <v>113.369</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>875.753</v>
+        <v>84.58199999999999</v>
+      </c>
+      <c r="H83" s="22" t="n">
+        <v>109.174</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>885.686</v>
+        <v>87.303</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>857.394</v>
+        <v>98.54300000000001</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>876.831</v>
+        <v>81.78400000000001</v>
+      </c>
+      <c r="L83" s="22" t="n">
+        <v>110.14</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>966.5</v>
+        <v>86.58</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>955.224</v>
+        <v>123.017</v>
+      </c>
+      <c r="T83" s="22" t="n">
+        <v>112.725</v>
+      </c>
+      <c r="U83" s="22" t="n">
+        <v>157.443</v>
+      </c>
+      <c r="V83" s="22" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="W83" s="22" t="n">
+        <v>109.174</v>
+      </c>
+      <c r="X83" s="22" t="n">
+        <v>110.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="n">
+        <v>1078.22</v>
+      </c>
+      <c r="E84" s="22" t="n">
+        <v>835.3150000000001</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>855.228</v>
+      </c>
+      <c r="G84" s="22" t="n">
+        <v>875.753</v>
+      </c>
+      <c r="I84" s="22" t="n">
+        <v>885.686</v>
+      </c>
+      <c r="J84" s="22" t="n">
+        <v>857.394</v>
+      </c>
+      <c r="K84" s="22" t="n">
+        <v>876.831</v>
+      </c>
+      <c r="M84" s="22" t="n">
+        <v>966.5</v>
+      </c>
+      <c r="N84" s="22" t="n">
+        <v>955.224</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr">
+        <is>
           <t>영업비용 합계</t>
         </is>
       </c>
-      <c r="C84" s="22" t="n">
+      <c r="C85" s="22" t="n">
         <v>2342.458</v>
       </c>
-      <c r="D84" s="22" t="n">
+      <c r="D85" s="22" t="n">
         <v>2237.136</v>
       </c>
-      <c r="E84" s="22" t="n">
+      <c r="E85" s="22" t="n">
         <v>2135.386</v>
       </c>
-      <c r="F84" s="22" t="n">
+      <c r="F85" s="22" t="n">
         <v>2217.663</v>
       </c>
-      <c r="G84" s="22" t="n">
+      <c r="G85" s="22" t="n">
         <v>2135.67</v>
       </c>
-      <c r="H84" s="22" t="n">
+      <c r="H85" s="22" t="n">
         <v>2064.902</v>
       </c>
-      <c r="I84" s="22" t="n">
+      <c r="I85" s="22" t="n">
         <v>2166.475</v>
       </c>
-      <c r="J84" s="22" t="n">
+      <c r="J85" s="22" t="n">
         <v>2107.947</v>
       </c>
-      <c r="K84" s="22" t="n">
+      <c r="K85" s="22" t="n">
         <v>2142.967</v>
       </c>
-      <c r="L84" s="22" t="n">
+      <c r="L85" s="22" t="n">
         <v>2216.139</v>
       </c>
-      <c r="M84" s="22" t="n">
+      <c r="M85" s="22" t="n">
         <v>2331.401</v>
       </c>
-      <c r="N84" s="22" t="n">
+      <c r="N85" s="22" t="n">
         <v>2383.461</v>
       </c>
-      <c r="T84" s="22" t="n">
+      <c r="T85" s="22" t="n">
         <v>1690.562</v>
       </c>
-      <c r="U84" s="22" t="n">
+      <c r="U85" s="22" t="n">
         <v>2159.658</v>
       </c>
-      <c r="V84" s="22" t="n">
+      <c r="V85" s="22" t="n">
         <v>2237.136</v>
       </c>
-      <c r="W84" s="22" t="n">
+      <c r="W85" s="22" t="n">
         <v>2064.902</v>
       </c>
-      <c r="X84" s="22" t="n">
+      <c r="X85" s="22" t="n">
         <v>2216.139</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="C85" s="12" t="n">
+      <c r="C86" s="12" t="n">
         <v>-28.824</v>
       </c>
-      <c r="D85" s="12" t="n">
+      <c r="D86" s="12" t="n">
         <v>99.068</v>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="E86" s="12" t="n">
         <v>385.589</v>
       </c>
-      <c r="F85" s="12" t="n">
+      <c r="F86" s="12" t="n">
         <v>197.013</v>
       </c>
-      <c r="G85" s="12" t="n">
+      <c r="G86" s="12" t="n">
         <v>237.399</v>
       </c>
-      <c r="H85" s="12" t="n">
+      <c r="H86" s="12" t="n">
         <v>407.327</v>
       </c>
-      <c r="I85" s="12" t="n">
+      <c r="I86" s="12" t="n">
         <v>279.952</v>
       </c>
-      <c r="J85" s="12" t="n">
+      <c r="J86" s="12" t="n">
         <v>220.017</v>
       </c>
-      <c r="K85" s="12" t="n">
+      <c r="K86" s="12" t="n">
         <v>370.769</v>
       </c>
-      <c r="L85" s="12" t="n">
+      <c r="L86" s="12" t="n">
         <v>470.403</v>
       </c>
-      <c r="M85" s="12" t="n">
+      <c r="M86" s="12" t="n">
         <v>424.426</v>
       </c>
-      <c r="N85" s="12" t="n">
+      <c r="N86" s="12" t="n">
         <v>423.711</v>
       </c>
-      <c r="T85" s="12" t="n">
+      <c r="T86" s="12" t="n">
         <v>139.656</v>
       </c>
-      <c r="U85" s="12" t="n">
+      <c r="U86" s="12" t="n">
         <v>-83.60599999999999</v>
       </c>
-      <c r="V85" s="12" t="n">
+      <c r="V86" s="12" t="n">
         <v>99.068</v>
       </c>
-      <c r="W85" s="12" t="n">
+      <c r="W86" s="12" t="n">
         <v>407.327</v>
       </c>
-      <c r="X85" s="12" t="n">
+      <c r="X86" s="12" t="n">
         <v>470.403</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>이자수익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>1.515</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>2.394</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>3.129</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>3.045</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>4.553</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>3.129</v>
-      </c>
-    </row>
     <row r="87">
-      <c r="A87" s="20" t="inlineStr">
-        <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C87" s="22" t="n">
-        <v>96.875</v>
-      </c>
-      <c r="D87" s="22" t="n">
-        <v>1.724</v>
-      </c>
-      <c r="E87" s="22" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="F87" s="22" t="n">
-        <v>2.247</v>
-      </c>
-      <c r="G87" s="22" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="H87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" s="22" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="U87" s="22" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="V87" s="22" t="n">
-        <v>1.724</v>
-      </c>
-      <c r="W87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" s="22" t="n">
-        <v>0</v>
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C87" s="17">
+        <f>IF(OR(C86="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C86/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D87" s="17">
+        <f>IF(OR(D86="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D86/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E87" s="17">
+        <f>IF(OR(E86="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E86/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F87" s="17">
+        <f>IF(OR(F86="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F86/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G87" s="17">
+        <f>IF(OR(G86="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G86/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H87" s="17">
+        <f>IF(OR(H86="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H86/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I87" s="17">
+        <f>IF(OR(I86="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I86/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J87" s="17">
+        <f>IF(OR(J86="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J86/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>IF(OR(K86="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K86/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L87" s="17">
+        <f>IF(OR(L86="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L86/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M87" s="17">
+        <f>IF(OR(M86="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M86/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N87" s="17">
+        <f>IF(OR(N86="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N86/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T87" s="17">
+        <f>IF(OR(T86="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T86/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U87" s="17">
+        <f>IF(OR(U86="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U86/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V87" s="17">
+        <f>IF(OR(V86="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V86/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W87" s="17">
+        <f>IF(OR(W86="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W86/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X87" s="17">
+        <f>IF(OR(X86="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X86/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="20" t="inlineStr">
-        <is>
-          <t>보험금 수익</t>
-        </is>
-      </c>
-      <c r="D88" s="22" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="H88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="22" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="W88" s="22" t="n">
-        <v>0</v>
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G88" s="17">
+        <f>IF(OR(G86="",C86=""),"",IF(C86&lt;=0,"",IFERROR(G86/C86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H88" s="17">
+        <f>IF(OR(H86="",D86=""),"",IF(D86&lt;=0,"",IFERROR(H86/D86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I88" s="17">
+        <f>IF(OR(I86="",E86=""),"",IF(E86&lt;=0,"",IFERROR(I86/E86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J88" s="17">
+        <f>IF(OR(J86="",F86=""),"",IF(F86&lt;=0,"",IFERROR(J86/F86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>IF(OR(K86="",G86=""),"",IF(G86&lt;=0,"",IFERROR(K86/G86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L88" s="17">
+        <f>IF(OR(L86="",H86=""),"",IF(H86&lt;=0,"",IFERROR(L86/H86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M88" s="17">
+        <f>IF(OR(M86="",I86=""),"",IF(I86&lt;=0,"",IFERROR(M86/I86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N88" s="17">
+        <f>IF(OR(N86="",J86=""),"",IF(J86&lt;=0,"",IFERROR(N86/J86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T88" s="17">
+        <f>IF(OR(T86="",S86=""),"",IF(S86&lt;=0,"",IFERROR(T86/S86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U88" s="17">
+        <f>IF(OR(U86="",T86=""),"",IF(T86&lt;=0,"",IFERROR(U86/T86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V88" s="17">
+        <f>IF(OR(V86="",U86=""),"",IF(U86&lt;=0,"",IFERROR(V86/U86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W88" s="17">
+        <f>IF(OR(W86="",V86=""),"",IF(V86&lt;=0,"",IFERROR(W86/V86-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X88" s="17">
+        <f>IF(OR(X86="",W86=""),"",IF(W86&lt;=0,"",IFERROR(X86/W86-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>임대료 수익</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>5.599</v>
+        <v>0.011</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>7.63</v>
+        <v>0.019</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>6.507</v>
+        <v>0.008</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>6.929</v>
+        <v>0.125</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>7.964</v>
+        <v>0.404</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>8.303000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>9.164999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>9.385</v>
+        <v>1.515</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>9.667999999999999</v>
+        <v>2.394</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>10.057</v>
+        <v>3.129</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>8.743</v>
+        <v>3.045</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>9.657</v>
+        <v>4.553</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>1.699</v>
+        <v>0.012</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>3.835</v>
+        <v>0.007</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>7.63</v>
+        <v>0.019</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>8.303000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="X89" s="22" t="n">
-        <v>10.057</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>채무 환입이익</t>
-        </is>
+          <t>보조금 수입</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="I90" s="22" t="n">
         <v>0</v>
@@ -6320,2540 +6417,2675 @@
       <c r="J90" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M90" s="22" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="N90" s="22" t="n">
-        <v>0.057</v>
+      <c r="K90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="22" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="U90" s="22" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>환급금 수익</t>
-        </is>
-      </c>
-      <c r="C91" s="22" t="n">
+          <t>보험금 수익</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="H91" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="22" t="n">
-        <v>59.691</v>
-      </c>
-      <c r="E91" s="22" t="n">
-        <v>36.286</v>
-      </c>
-      <c r="F91" s="22" t="n">
-        <v>1.103</v>
-      </c>
-      <c r="G91" s="22" t="n">
-        <v>-0.866</v>
-      </c>
-      <c r="H91" s="22" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="J91" s="22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>45.924</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="N91" s="22" t="n">
-        <v>0.001</v>
+      <c r="U91" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V91" s="22" t="n">
-        <v>59.691</v>
+        <v>0.546</v>
       </c>
       <c r="W91" s="22" t="n">
-        <v>0.779</v>
-      </c>
-      <c r="X91" s="22" t="n">
-        <v>0.469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>외환차익</t>
-        </is>
+          <t>임대료 수익</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>5.599</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>7.63</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>0</v>
+        <v>6.507</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>0</v>
+        <v>6.929</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>7.964</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>8.303000000000001</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>23.367</v>
+        <v>9.164999999999999</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>-15.933</v>
+        <v>9.385</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>9.667999999999999</v>
+      </c>
+      <c r="L92" s="22" t="n">
+        <v>10.057</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>0</v>
+        <v>8.743</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>0</v>
+        <v>9.657</v>
+      </c>
+      <c r="T92" s="22" t="n">
+        <v>1.699</v>
+      </c>
+      <c r="U92" s="22" t="n">
+        <v>3.835</v>
+      </c>
+      <c r="V92" s="22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="W92" s="22" t="n">
+        <v>8.303000000000001</v>
+      </c>
+      <c r="X92" s="22" t="n">
+        <v>10.057</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C93" s="22" t="n">
-        <v>2.861</v>
-      </c>
-      <c r="D93" s="22" t="n">
-        <v>5.338</v>
-      </c>
-      <c r="E93" s="22" t="n">
-        <v>3.058</v>
-      </c>
-      <c r="F93" s="22" t="n">
-        <v>2.341</v>
-      </c>
-      <c r="G93" s="22" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="H93" s="22" t="n">
-        <v>-5.208</v>
+          <t>채무 환입이익</t>
+        </is>
       </c>
       <c r="I93" s="22" t="n">
-        <v>3.015</v>
+        <v>0</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>3.131</v>
-      </c>
-      <c r="K93" s="22" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="L93" s="22" t="n">
-        <v>4.986</v>
+        <v>0</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>3.149</v>
+        <v>6.71</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>2.629</v>
-      </c>
-      <c r="U93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V93" s="22" t="n">
-        <v>5.338</v>
-      </c>
-      <c r="W93" s="22" t="n">
-        <v>-5.208</v>
-      </c>
-      <c r="X93" s="22" t="n">
-        <v>4.986</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>환급금 수익</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>136.098</v>
+        <v>0</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>74.949</v>
+        <v>59.691</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>46.194</v>
+        <v>36.286</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>12.746</v>
+        <v>1.103</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>8.228999999999999</v>
+        <v>-0.866</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>4.4</v>
+        <v>0.779</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>37.181</v>
+        <v>0.221</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>-1.9</v>
+        <v>0.003</v>
       </c>
       <c r="K94" s="22" t="n">
-        <v>50.642</v>
+        <v>45.924</v>
       </c>
       <c r="L94" s="22" t="n">
-        <v>44.3</v>
+        <v>0.469</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>21.732</v>
+        <v>0.082</v>
       </c>
       <c r="N94" s="22" t="n">
-        <v>16.896</v>
-      </c>
-      <c r="T94" s="22" t="n">
-        <v>-0.182</v>
-      </c>
-      <c r="U94" s="22" t="n">
-        <v>4.237</v>
+        <v>0.001</v>
       </c>
       <c r="V94" s="22" t="n">
-        <v>74.949</v>
+        <v>59.691</v>
       </c>
       <c r="W94" s="22" t="n">
-        <v>4.4</v>
+        <v>0.779</v>
       </c>
       <c r="X94" s="22" t="n">
-        <v>44.3</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n">
-        <v>8.946</v>
-      </c>
-      <c r="D95" s="22" t="n">
-        <v>8.973000000000001</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="E95" s="22" t="n">
-        <v>9.512</v>
+        <v>0</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>10.301</v>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>11.116</v>
-      </c>
-      <c r="H95" s="22" t="n">
-        <v>12.739</v>
+        <v>0</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>14.039</v>
+        <v>23.367</v>
       </c>
       <c r="J95" s="22" t="n">
-        <v>13.506</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>12.737</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>12.7</v>
+        <v>-15.933</v>
       </c>
       <c r="M95" s="22" t="n">
-        <v>13.953</v>
+        <v>0</v>
       </c>
       <c r="N95" s="22" t="n">
-        <v>11.506</v>
-      </c>
-      <c r="T95" s="22" t="n">
-        <v>11.62</v>
-      </c>
-      <c r="U95" s="22" t="n">
-        <v>10.207</v>
-      </c>
-      <c r="V95" s="22" t="n">
-        <v>8.973000000000001</v>
-      </c>
-      <c r="W95" s="22" t="n">
-        <v>12.739</v>
-      </c>
-      <c r="X95" s="22" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>2.028</v>
+        <v>2.861</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>2.338</v>
+        <v>5.338</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>2.549</v>
+        <v>3.058</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>8.56</v>
+        <v>2.341</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>-1.369</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>-8.595000000000001</v>
+        <v>-5.208</v>
       </c>
       <c r="I96" s="22" t="n">
+        <v>3.015</v>
+      </c>
+      <c r="J96" s="22" t="n">
+        <v>3.131</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>4.986</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>3.149</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="U96" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="22" t="n">
-        <v>7.734</v>
-      </c>
-      <c r="L96" s="22" t="n">
-        <v>-1.334</v>
-      </c>
-      <c r="M96" s="22" t="n">
-        <v>10.415</v>
-      </c>
-      <c r="N96" s="22" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="T96" s="22" t="n">
-        <v>2.017</v>
-      </c>
-      <c r="U96" s="22" t="n">
-        <v>-1.532</v>
-      </c>
       <c r="V96" s="22" t="n">
-        <v>2.338</v>
+        <v>5.338</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>-8.595000000000001</v>
+        <v>-5.208</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>-1.334</v>
+        <v>4.986</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>자금조달비용</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n">
+        <v>136.098</v>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>74.949</v>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>46.194</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>8.228999999999999</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>37.181</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>50.642</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>21.732</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>16.896</v>
       </c>
       <c r="T97" s="22" t="n">
-        <v>0</v>
+        <v>-0.182</v>
       </c>
       <c r="U97" s="22" t="n">
-        <v>0</v>
+        <v>4.237</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>74.949</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>44.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>판매세 반환손실</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>0</v>
+        <v>8.946</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>0</v>
+        <v>8.973000000000001</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>41.048</v>
+        <v>9.512</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>0.984</v>
+        <v>10.301</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>-0.265</v>
+        <v>11.116</v>
       </c>
       <c r="H98" s="22" t="n">
-        <v>0.08</v>
+        <v>12.739</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>0</v>
+        <v>14.039</v>
       </c>
       <c r="J98" s="22" t="n">
-        <v>0</v>
+        <v>13.506</v>
       </c>
       <c r="K98" s="22" t="n">
-        <v>0</v>
+        <v>12.737</v>
       </c>
       <c r="L98" s="22" t="n">
-        <v>0</v>
+        <v>12.7</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>13.953</v>
+      </c>
+      <c r="N98" s="22" t="n">
+        <v>11.506</v>
+      </c>
+      <c r="T98" s="22" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="U98" s="22" t="n">
+        <v>10.207</v>
       </c>
       <c r="V98" s="22" t="n">
-        <v>0</v>
+        <v>8.973000000000001</v>
       </c>
       <c r="W98" s="22" t="n">
-        <v>0.08</v>
+        <v>12.739</v>
       </c>
       <c r="X98" s="22" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
-        <v>0.004</v>
+        <v>2.028</v>
       </c>
       <c r="D99" s="22" t="n">
-        <v>0.003</v>
+        <v>2.338</v>
       </c>
       <c r="E99" s="22" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>-1.369</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>-8.595000000000001</v>
+      </c>
+      <c r="I99" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G99" s="22" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="H99" s="22" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="I99" s="22" t="n">
-        <v>3.923</v>
-      </c>
       <c r="J99" s="22" t="n">
-        <v>-0.103</v>
+        <v>0</v>
       </c>
       <c r="K99" s="22" t="n">
-        <v>3.309</v>
+        <v>7.734</v>
       </c>
       <c r="L99" s="22" t="n">
-        <v>-7.108</v>
+        <v>-1.334</v>
       </c>
       <c r="M99" s="22" t="n">
-        <v>0.129</v>
+        <v>10.415</v>
       </c>
       <c r="N99" s="22" t="n">
-        <v>0.001</v>
+        <v>0.272</v>
       </c>
       <c r="T99" s="22" t="n">
-        <v>1.298</v>
+        <v>2.017</v>
       </c>
       <c r="U99" s="22" t="n">
-        <v>0.587</v>
+        <v>-1.532</v>
       </c>
       <c r="V99" s="22" t="n">
-        <v>0.003</v>
+        <v>2.338</v>
       </c>
       <c r="W99" s="22" t="n">
-        <v>0.354</v>
+        <v>-8.595000000000001</v>
       </c>
       <c r="X99" s="22" t="n">
-        <v>-7.108</v>
+        <v>-1.334</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>10.978</v>
-      </c>
-      <c r="D100" s="22" t="n">
-        <v>11.314</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>53.11</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>19.866</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>9.489000000000001</v>
-      </c>
-      <c r="H100" s="22" t="n">
-        <v>4.578</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>17.962</v>
-      </c>
-      <c r="J100" s="22" t="n">
-        <v>13.403</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>23.782</v>
-      </c>
-      <c r="L100" s="22" t="n">
-        <v>11.813</v>
-      </c>
-      <c r="M100" s="22" t="n">
-        <v>24.499</v>
-      </c>
-      <c r="N100" s="22" t="n">
-        <v>11.778</v>
+          <t>자금조달비용</t>
+        </is>
       </c>
       <c r="T100" s="22" t="n">
-        <v>14.936</v>
+        <v>0</v>
       </c>
       <c r="U100" s="22" t="n">
-        <v>9.263</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>11.314</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>4.578</v>
-      </c>
-      <c r="X100" s="22" t="n">
-        <v>11.813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>96.297</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>162.701</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>378.674</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>189.892</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>236.139</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>407.149</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>299.171</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>204.714</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>397.629</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>502.889</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>421.659</v>
-      </c>
-      <c r="N101" s="12" t="n">
-        <v>428.829</v>
-      </c>
-      <c r="T101" s="12" t="n">
-        <v>124.538</v>
-      </c>
-      <c r="U101" s="12" t="n">
-        <v>-88.631</v>
-      </c>
-      <c r="V101" s="12" t="n">
-        <v>162.701</v>
-      </c>
-      <c r="W101" s="12" t="n">
-        <v>407.149</v>
-      </c>
-      <c r="X101" s="12" t="n">
-        <v>502.889</v>
+      <c r="A101" s="20" t="inlineStr">
+        <is>
+          <t>판매세 반환손실</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22" t="n">
+        <v>41.048</v>
+      </c>
+      <c r="F101" s="22" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="G101" s="22" t="n">
+        <v>-0.265</v>
+      </c>
+      <c r="H101" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="X101" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>손상차손</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C102" s="22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E102" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="22" t="n">
-        <v>14472.936</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>195.444</v>
-      </c>
       <c r="F102" s="22" t="n">
-        <v>68.009</v>
+        <v>0.02</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>63.019</v>
+        <v>0.008</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>72.483</v>
+        <v>0.354</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>76.014</v>
+        <v>3.923</v>
       </c>
       <c r="J102" s="22" t="n">
-        <v>61.181</v>
+        <v>-0.103</v>
       </c>
       <c r="K102" s="22" t="n">
-        <v>47.16</v>
+        <v>3.309</v>
       </c>
       <c r="L102" s="22" t="n">
-        <v>69.78</v>
+        <v>-7.108</v>
       </c>
       <c r="M102" s="22" t="n">
-        <v>66.61199999999999</v>
+        <v>0.129</v>
       </c>
       <c r="N102" s="22" t="n">
-        <v>61.417</v>
+        <v>0.001</v>
+      </c>
+      <c r="T102" s="22" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="U102" s="22" t="n">
+        <v>0.587</v>
       </c>
       <c r="V102" s="22" t="n">
-        <v>14472.936</v>
+        <v>0.003</v>
       </c>
       <c r="W102" s="22" t="n">
-        <v>72.483</v>
+        <v>0.354</v>
       </c>
       <c r="X102" s="22" t="n">
-        <v>69.78</v>
+        <v>-7.108</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>0</v>
+        <v>10.978</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>0</v>
+        <v>11.314</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>0</v>
+        <v>53.11</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>0</v>
+        <v>19.866</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>0</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>0.08599999999999999</v>
+        <v>4.578</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>0.52</v>
+        <v>17.962</v>
       </c>
       <c r="J103" s="22" t="n">
-        <v>0</v>
+        <v>13.403</v>
       </c>
       <c r="K103" s="22" t="n">
-        <v>0</v>
+        <v>23.782</v>
       </c>
       <c r="L103" s="22" t="n">
-        <v>0</v>
+        <v>11.813</v>
       </c>
       <c r="M103" s="22" t="n">
-        <v>0</v>
+        <v>24.499</v>
       </c>
       <c r="N103" s="22" t="n">
-        <v>0</v>
+        <v>11.778</v>
+      </c>
+      <c r="T103" s="22" t="n">
+        <v>14.936</v>
+      </c>
+      <c r="U103" s="22" t="n">
+        <v>9.263</v>
       </c>
       <c r="V103" s="22" t="n">
-        <v>0</v>
+        <v>11.314</v>
       </c>
       <c r="W103" s="22" t="n">
-        <v>0.08599999999999999</v>
+        <v>4.578</v>
       </c>
       <c r="X103" s="22" t="n">
-        <v>0</v>
+        <v>11.813</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>특별손실 합계</t>
-        </is>
-      </c>
-      <c r="C104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="22" t="n">
-        <v>14505.405</v>
-      </c>
-      <c r="E104" s="22" t="n">
-        <v>195.444</v>
-      </c>
-      <c r="F104" s="22" t="n">
-        <v>68.009</v>
-      </c>
-      <c r="G104" s="22" t="n">
-        <v>63.019</v>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>72.569</v>
-      </c>
-      <c r="I104" s="22" t="n">
-        <v>76.535</v>
-      </c>
-      <c r="J104" s="22" t="n">
-        <v>61.181</v>
-      </c>
-      <c r="K104" s="22" t="n">
-        <v>47.16</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>69.78</v>
-      </c>
-      <c r="M104" s="22" t="n">
-        <v>66.61199999999999</v>
-      </c>
-      <c r="N104" s="22" t="n">
-        <v>61.417</v>
-      </c>
-      <c r="V104" s="22" t="n">
-        <v>14505.405</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>72.569</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>69.78</v>
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>96.297</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>162.701</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>378.674</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>189.892</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>236.139</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>407.149</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>299.171</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>204.714</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>397.629</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>502.889</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>421.659</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>428.829</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>124.538</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>-88.631</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>162.701</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>407.149</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>502.889</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>96.297</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>-14342.703</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>183.23</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>121.882</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>173.121</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>334.58</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>222.635</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>143.534</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>350.469</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>433.109</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>355.047</v>
-      </c>
-      <c r="N105" s="12" t="n">
-        <v>397.331</v>
-      </c>
-      <c r="T105" s="12" t="n">
-        <v>124.538</v>
-      </c>
-      <c r="U105" s="12" t="n">
-        <v>-88.631</v>
-      </c>
-      <c r="V105" s="12" t="n">
-        <v>-14342.703</v>
-      </c>
-      <c r="W105" s="12" t="n">
-        <v>334.58</v>
-      </c>
-      <c r="X105" s="12" t="n">
-        <v>433.109</v>
+      <c r="A105" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G105" s="17">
+        <f>IF(OR(G104="",C104=""),"",IF(C104&lt;=0,"",IFERROR(G104/C104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H105" s="17">
+        <f>IF(OR(H104="",D104=""),"",IF(D104&lt;=0,"",IFERROR(H104/D104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I105" s="17">
+        <f>IF(OR(I104="",E104=""),"",IF(E104&lt;=0,"",IFERROR(I104/E104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J105" s="17">
+        <f>IF(OR(J104="",F104=""),"",IF(F104&lt;=0,"",IFERROR(J104/F104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF(OR(K104="",G104=""),"",IF(G104&lt;=0,"",IFERROR(K104/G104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L105" s="17">
+        <f>IF(OR(L104="",H104=""),"",IF(H104&lt;=0,"",IFERROR(L104/H104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M105" s="17">
+        <f>IF(OR(M104="",I104=""),"",IF(I104&lt;=0,"",IFERROR(M104/I104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N105" s="17">
+        <f>IF(OR(N104="",J104=""),"",IF(J104&lt;=0,"",IFERROR(N104/J104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T105" s="17">
+        <f>IF(OR(T104="",S104=""),"",IF(S104&lt;=0,"",IFERROR(T104/S104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U105" s="17">
+        <f>IF(OR(U104="",T104=""),"",IF(T104&lt;=0,"",IFERROR(U104/T104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V105" s="17">
+        <f>IF(OR(V104="",U104=""),"",IF(U104&lt;=0,"",IFERROR(V104/U104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W105" s="17">
+        <f>IF(OR(W104="",V104=""),"",IF(V104&lt;=0,"",IFERROR(W104/V104-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X105" s="17">
+        <f>IF(OR(X104="",W104=""),"",IF(W104&lt;=0,"",IFERROR(X104/W104-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C106" s="22" t="n">
-        <v>134.327</v>
+        <v>0</v>
       </c>
       <c r="D106" s="22" t="n">
-        <v>123.086</v>
+        <v>14472.936</v>
       </c>
       <c r="E106" s="22" t="n">
-        <v>50.76</v>
+        <v>195.444</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>90.57299999999999</v>
+        <v>68.009</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>123.997</v>
+        <v>63.019</v>
       </c>
       <c r="H106" s="22" t="n">
-        <v>73.346</v>
+        <v>72.483</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>65.158</v>
+        <v>76.014</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>78.93600000000001</v>
+        <v>61.181</v>
       </c>
       <c r="K106" s="22" t="n">
-        <v>54.235</v>
+        <v>47.16</v>
       </c>
       <c r="L106" s="22" t="n">
-        <v>128.914</v>
+        <v>69.78</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>61.87</v>
+        <v>66.61199999999999</v>
       </c>
       <c r="N106" s="22" t="n">
-        <v>180.437</v>
-      </c>
-      <c r="T106" s="22" t="n">
-        <v>145.14</v>
-      </c>
-      <c r="U106" s="22" t="n">
-        <v>40.87</v>
+        <v>61.417</v>
       </c>
       <c r="V106" s="22" t="n">
-        <v>123.086</v>
+        <v>14472.936</v>
       </c>
       <c r="W106" s="22" t="n">
-        <v>73.346</v>
+        <v>72.483</v>
       </c>
       <c r="X106" s="22" t="n">
-        <v>128.914</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>-65.203</v>
+        <v>0</v>
       </c>
       <c r="D107" s="22" t="n">
-        <v>-1999.336</v>
+        <v>0</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>71.92700000000001</v>
+        <v>0</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>-15.486</v>
+        <v>0</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>-39.748</v>
+        <v>0</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>-19.801</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>75.78</v>
+        <v>0.52</v>
       </c>
       <c r="J107" s="22" t="n">
-        <v>-35.354</v>
+        <v>0</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>-25.353</v>
+        <v>0</v>
       </c>
       <c r="L107" s="22" t="n">
-        <v>-84.47</v>
+        <v>0</v>
       </c>
       <c r="M107" s="22" t="n">
-        <v>66.76300000000001</v>
+        <v>0</v>
       </c>
       <c r="N107" s="22" t="n">
-        <v>-45.743</v>
-      </c>
-      <c r="T107" s="22" t="n">
-        <v>-86.289</v>
-      </c>
-      <c r="U107" s="22" t="n">
-        <v>-295.229</v>
+        <v>0</v>
       </c>
       <c r="V107" s="22" t="n">
-        <v>-1999.336</v>
+        <v>0</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>-19.801</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="X107" s="22" t="n">
-        <v>-84.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
+          <t>특별손실 합계</t>
         </is>
       </c>
       <c r="C108" s="22" t="n">
-        <v>69.124</v>
+        <v>0</v>
       </c>
       <c r="D108" s="22" t="n">
-        <v>-1876.248</v>
+        <v>14505.405</v>
       </c>
       <c r="E108" s="22" t="n">
-        <v>122.688</v>
+        <v>195.444</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>75.087</v>
+        <v>68.009</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>84.249</v>
+        <v>63.019</v>
       </c>
       <c r="H108" s="22" t="n">
-        <v>53.544</v>
+        <v>72.569</v>
       </c>
       <c r="I108" s="22" t="n">
-        <v>140.938</v>
+        <v>76.535</v>
       </c>
       <c r="J108" s="22" t="n">
-        <v>43.582</v>
+        <v>61.181</v>
       </c>
       <c r="K108" s="22" t="n">
-        <v>28.882</v>
+        <v>47.16</v>
       </c>
       <c r="L108" s="22" t="n">
-        <v>44.443</v>
+        <v>69.78</v>
       </c>
       <c r="M108" s="22" t="n">
-        <v>128.634</v>
+        <v>66.61199999999999</v>
       </c>
       <c r="N108" s="22" t="n">
-        <v>134.694</v>
-      </c>
-      <c r="T108" s="22" t="n">
-        <v>58.851</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>-254.358</v>
+        <v>61.417</v>
       </c>
       <c r="V108" s="22" t="n">
-        <v>-1876.248</v>
+        <v>14505.405</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>53.544</v>
+        <v>72.569</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>44.443</v>
+        <v>69.78</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>96.297</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>-14342.703</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>183.23</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>121.882</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>173.121</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>222.635</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>143.534</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>350.469</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>433.109</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>355.047</v>
+      </c>
+      <c r="N109" s="12" t="n">
+        <v>397.331</v>
+      </c>
+      <c r="T109" s="12" t="n">
+        <v>124.538</v>
+      </c>
+      <c r="U109" s="12" t="n">
+        <v>-88.631</v>
+      </c>
+      <c r="V109" s="12" t="n">
+        <v>-14342.703</v>
+      </c>
+      <c r="W109" s="12" t="n">
+        <v>334.58</v>
+      </c>
+      <c r="X109" s="12" t="n">
+        <v>433.109</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>134.327</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>123.086</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="F110" s="22" t="n">
+        <v>90.57299999999999</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>123.997</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>73.346</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>65.158</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>78.93600000000001</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>54.235</v>
+      </c>
+      <c r="L110" s="22" t="n">
+        <v>128.914</v>
+      </c>
+      <c r="M110" s="22" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>180.437</v>
+      </c>
+      <c r="T110" s="22" t="n">
+        <v>145.14</v>
+      </c>
+      <c r="U110" s="22" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>123.086</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>73.346</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>128.914</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n">
+        <v>-65.203</v>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>-1999.336</v>
+      </c>
+      <c r="E111" s="22" t="n">
+        <v>71.92700000000001</v>
+      </c>
+      <c r="F111" s="22" t="n">
+        <v>-15.486</v>
+      </c>
+      <c r="G111" s="22" t="n">
+        <v>-39.748</v>
+      </c>
+      <c r="H111" s="22" t="n">
+        <v>-19.801</v>
+      </c>
+      <c r="I111" s="22" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="J111" s="22" t="n">
+        <v>-35.354</v>
+      </c>
+      <c r="K111" s="22" t="n">
+        <v>-25.353</v>
+      </c>
+      <c r="L111" s="22" t="n">
+        <v>-84.47</v>
+      </c>
+      <c r="M111" s="22" t="n">
+        <v>66.76300000000001</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>-45.743</v>
+      </c>
+      <c r="T111" s="22" t="n">
+        <v>-86.289</v>
+      </c>
+      <c r="U111" s="22" t="n">
+        <v>-295.229</v>
+      </c>
+      <c r="V111" s="22" t="n">
+        <v>-1999.336</v>
+      </c>
+      <c r="W111" s="22" t="n">
+        <v>-19.801</v>
+      </c>
+      <c r="X111" s="22" t="n">
+        <v>-84.47</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>69.124</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>-1876.248</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>122.688</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>75.087</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>84.249</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>53.544</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>140.938</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>43.582</v>
+      </c>
+      <c r="K112" s="22" t="n">
+        <v>28.882</v>
+      </c>
+      <c r="L112" s="22" t="n">
+        <v>44.443</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>128.634</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>134.694</v>
+      </c>
+      <c r="T112" s="22" t="n">
+        <v>58.851</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>-254.358</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>-1876.248</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>53.544</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>44.443</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C109" s="12" t="n">
+      <c r="C113" s="12" t="n">
         <v>27.172</v>
       </c>
-      <c r="D109" s="12" t="n">
+      <c r="D113" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="E109" s="12" t="n">
+      <c r="E113" s="12" t="n">
         <v>60.542</v>
       </c>
-      <c r="F109" s="12" t="n">
+      <c r="F113" s="12" t="n">
         <v>46.795</v>
       </c>
-      <c r="G109" s="12" t="n">
+      <c r="G113" s="12" t="n">
         <v>88.872</v>
       </c>
-      <c r="H109" s="12" t="n">
+      <c r="H113" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="I109" s="12" t="n">
+      <c r="I113" s="12" t="n">
         <v>81.697</v>
       </c>
-      <c r="J109" s="12" t="n">
+      <c r="J113" s="12" t="n">
         <v>99.95099999999999</v>
       </c>
-      <c r="K109" s="12" t="n">
+      <c r="K113" s="12" t="n">
         <v>321.587</v>
       </c>
-      <c r="L109" s="12" t="n">
+      <c r="L113" s="12" t="n">
         <v>388.666</v>
       </c>
-      <c r="M109" s="12" t="n">
+      <c r="M113" s="12" t="n">
         <v>226.412</v>
       </c>
-      <c r="N109" s="12" t="n">
+      <c r="N113" s="12" t="n">
         <v>262.637</v>
       </c>
-      <c r="T109" s="12" t="n">
+      <c r="T113" s="12" t="n">
         <v>65.687</v>
       </c>
-      <c r="U109" s="12" t="n">
+      <c r="U113" s="12" t="n">
         <v>165.726</v>
       </c>
-      <c r="V109" s="12" t="n">
+      <c r="V113" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="W109" s="12" t="n">
+      <c r="W113" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="X109" s="12" t="n">
+      <c r="X113" s="12" t="n">
         <v>388.666</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G114" s="17">
+        <f>IF(OR(G113="",C113=""),"",IF(C113&lt;=0,"",IFERROR(G113/C113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H114" s="17">
+        <f>IF(OR(H113="",D113=""),"",IF(D113&lt;=0,"",IFERROR(H113/D113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I114" s="17">
+        <f>IF(OR(I113="",E113=""),"",IF(E113&lt;=0,"",IFERROR(I113/E113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J114" s="17">
+        <f>IF(OR(J113="",F113=""),"",IF(F113&lt;=0,"",IFERROR(J113/F113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF(OR(K113="",G113=""),"",IF(G113&lt;=0,"",IFERROR(K113/G113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L114" s="17">
+        <f>IF(OR(L113="",H113=""),"",IF(H113&lt;=0,"",IFERROR(L113/H113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M114" s="17">
+        <f>IF(OR(M113="",I113=""),"",IF(I113&lt;=0,"",IFERROR(M113/I113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N114" s="17">
+        <f>IF(OR(N113="",J113=""),"",IF(J113&lt;=0,"",IFERROR(N113/J113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T114" s="17">
+        <f>IF(OR(T113="",S113=""),"",IF(S113&lt;=0,"",IFERROR(T113/S113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U114" s="17">
+        <f>IF(OR(U113="",T113=""),"",IF(T113&lt;=0,"",IFERROR(U113/T113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V114" s="17">
+        <f>IF(OR(V113="",U113=""),"",IF(U113&lt;=0,"",IFERROR(V113/U113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W114" s="17">
+        <f>IF(OR(W113="",V113=""),"",IF(V113&lt;=0,"",IFERROR(W113/V113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X114" s="17">
+        <f>IF(OR(X113="",W113=""),"",IF(W113&lt;=0,"",IFERROR(X113/W113-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C110" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>27.172</v>
       </c>
-      <c r="D110" s="12" t="n">
+      <c r="D115" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>60.542</v>
       </c>
-      <c r="F110" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>46.795</v>
       </c>
-      <c r="G110" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>88.872</v>
       </c>
-      <c r="H110" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="I110" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>81.697</v>
       </c>
-      <c r="J110" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>99.95099999999999</v>
       </c>
-      <c r="K110" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>321.587</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>388.666</v>
       </c>
-      <c r="M110" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>226.412</v>
       </c>
-      <c r="N110" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>262.637</v>
       </c>
-      <c r="T110" s="12" t="n">
+      <c r="T115" s="12" t="n">
         <v>65.687</v>
       </c>
-      <c r="U110" s="12" t="n">
+      <c r="U115" s="12" t="n">
         <v>165.726</v>
       </c>
-      <c r="V110" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="W110" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="X110" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>388.666</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="18" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G116" s="17">
+        <f>IF(OR(G115="",C115=""),"",IF(C115&lt;=0,"",IFERROR(G115/C115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H116" s="17">
+        <f>IF(OR(H115="",D115=""),"",IF(D115&lt;=0,"",IFERROR(H115/D115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I116" s="17">
+        <f>IF(OR(I115="",E115=""),"",IF(E115&lt;=0,"",IFERROR(I115/E115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J116" s="17">
+        <f>IF(OR(J115="",F115=""),"",IF(F115&lt;=0,"",IFERROR(J115/F115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF(OR(K115="",G115=""),"",IF(G115&lt;=0,"",IFERROR(K115/G115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L116" s="17">
+        <f>IF(OR(L115="",H115=""),"",IF(H115&lt;=0,"",IFERROR(L115/H115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M116" s="17">
+        <f>IF(OR(M115="",I115=""),"",IF(I115&lt;=0,"",IFERROR(M115/I115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="17">
+        <f>IF(OR(N115="",J115=""),"",IF(J115&lt;=0,"",IFERROR(N115/J115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T116" s="17">
+        <f>IF(OR(T115="",S115=""),"",IF(S115&lt;=0,"",IFERROR(T115/S115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U116" s="17">
+        <f>IF(OR(U115="",T115=""),"",IF(T115&lt;=0,"",IFERROR(U115/T115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V116" s="17">
+        <f>IF(OR(V115="",U115=""),"",IF(U115&lt;=0,"",IFERROR(V115/U115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W116" s="17">
+        <f>IF(OR(W115="",V115=""),"",IF(V115&lt;=0,"",IFERROR(W115/V115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X116" s="17">
+        <f>IF(OR(X115="",W115=""),"",IF(W115&lt;=0,"",IFERROR(X115/W115-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B112" s="44" t="inlineStr">
+      <c r="B118" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-      <c r="J112" s="18" t="n"/>
-      <c r="K112" s="18" t="n"/>
-      <c r="L112" s="18" t="n"/>
-      <c r="M112" s="18" t="n"/>
-      <c r="N112" s="18" t="n"/>
-      <c r="O112" s="18" t="n"/>
-      <c r="P112" s="18" t="n"/>
-      <c r="Q112" s="18" t="n"/>
-      <c r="R112" s="18" t="n"/>
-      <c r="S112" s="18" t="n"/>
-      <c r="T112" s="18" t="n"/>
-      <c r="U112" s="18" t="n"/>
-      <c r="V112" s="18" t="n"/>
-      <c r="W112" s="18" t="n"/>
-      <c r="X112" s="18" t="n"/>
-      <c r="Y112" s="18" t="n"/>
-      <c r="Z112" s="18" t="n"/>
-      <c r="AA112" s="18" t="n"/>
-      <c r="AB112" s="18" t="n"/>
-      <c r="AC112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
+      <c r="L118" s="18" t="n"/>
+      <c r="M118" s="18" t="n"/>
+      <c r="N118" s="18" t="n"/>
+      <c r="O118" s="18" t="n"/>
+      <c r="P118" s="18" t="n"/>
+      <c r="Q118" s="18" t="n"/>
+      <c r="R118" s="18" t="n"/>
+      <c r="S118" s="18" t="n"/>
+      <c r="T118" s="18" t="n"/>
+      <c r="U118" s="18" t="n"/>
+      <c r="V118" s="18" t="n"/>
+      <c r="W118" s="18" t="n"/>
+      <c r="X118" s="18" t="n"/>
+      <c r="Y118" s="18" t="n"/>
+      <c r="Z118" s="18" t="n"/>
+      <c r="AA118" s="18" t="n"/>
+      <c r="AB118" s="18" t="n"/>
+      <c r="AC118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="J113" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="K113" s="5" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="N113" s="5" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t>2027.2Q</t>
         </is>
       </c>
-      <c r="O113" s="5" t="inlineStr">
+      <c r="O119" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P113" s="5" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q113" s="5" t="inlineStr">
+      <c r="Q119" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R113" s="5" t="inlineStr">
+      <c r="R119" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S113" s="5" t="inlineStr">
+      <c r="S119" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T113" s="5" t="inlineStr">
+      <c r="T119" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U113" s="5" t="inlineStr">
+      <c r="U119" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V113" s="5" t="inlineStr">
+      <c r="V119" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W113" s="5" t="inlineStr">
+      <c r="W119" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X113" s="5" t="inlineStr">
+      <c r="X119" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y113" s="5" t="inlineStr">
+      <c r="Y119" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z113" s="5" t="inlineStr">
+      <c r="Z119" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA113" s="5" t="inlineStr">
+      <c r="AA119" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB113" s="5" t="inlineStr">
+      <c r="AB119" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC113" s="5" t="inlineStr">
+      <c r="AC119" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C120" s="12" t="n">
         <v>27.172</v>
       </c>
-      <c r="D114" s="12" t="n">
+      <c r="D120" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="E120" s="12" t="n">
         <v>60.542</v>
       </c>
-      <c r="F114" s="12" t="n">
+      <c r="F120" s="12" t="n">
         <v>46.795</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="G120" s="12" t="n">
         <v>88.872</v>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="I114" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>81.697</v>
       </c>
-      <c r="J114" s="12" t="n">
+      <c r="J120" s="12" t="n">
         <v>99.95099999999999</v>
       </c>
-      <c r="K114" s="12" t="n">
+      <c r="K120" s="12" t="n">
         <v>321.587</v>
       </c>
-      <c r="L114" s="12" t="n">
+      <c r="L120" s="12" t="n">
         <v>388.666</v>
       </c>
-      <c r="M114" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>226.412</v>
       </c>
-      <c r="N114" s="12" t="n">
+      <c r="N120" s="12" t="n">
         <v>262.637</v>
       </c>
-      <c r="T114" s="12" t="n">
+      <c r="T120" s="12" t="n">
         <v>65.687</v>
       </c>
-      <c r="U114" s="12" t="n">
+      <c r="U120" s="12" t="n">
         <v>165.726</v>
       </c>
-      <c r="V114" s="12" t="n">
+      <c r="V120" s="12" t="n">
         <v>-12466.454</v>
       </c>
-      <c r="W114" s="12" t="n">
+      <c r="W120" s="12" t="n">
         <v>281.036</v>
       </c>
-      <c r="X114" s="12" t="n">
+      <c r="X120" s="12" t="n">
         <v>388.666</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>해외사업환산조정</t>
         </is>
       </c>
-      <c r="C115" s="22" t="n">
+      <c r="C121" s="22" t="n">
         <v>449.733</v>
       </c>
-      <c r="D115" s="22" t="n">
+      <c r="D121" s="22" t="n">
         <v>-840.002</v>
       </c>
-      <c r="E115" s="22" t="n">
+      <c r="E121" s="22" t="n">
         <v>60.963</v>
       </c>
-      <c r="F115" s="22" t="n">
+      <c r="F121" s="22" t="n">
         <v>24.694</v>
       </c>
-      <c r="G115" s="22" t="n">
+      <c r="G121" s="22" t="n">
         <v>-68.005</v>
       </c>
-      <c r="H115" s="22" t="n">
+      <c r="H121" s="22" t="n">
         <v>49.592</v>
       </c>
-      <c r="I115" s="22" t="n">
+      <c r="I121" s="22" t="n">
         <v>-25.084</v>
       </c>
-      <c r="J115" s="22" t="n">
+      <c r="J121" s="22" t="n">
         <v>-16.655</v>
       </c>
-      <c r="K115" s="22" t="n">
+      <c r="K121" s="22" t="n">
         <v>54.819</v>
       </c>
-      <c r="L115" s="22" t="n">
+      <c r="L121" s="22" t="n">
         <v>30.288</v>
       </c>
-      <c r="M115" s="22" t="n">
+      <c r="M121" s="22" t="n">
         <v>7.724</v>
       </c>
-      <c r="N115" s="22" t="n">
+      <c r="N121" s="22" t="n">
         <v>-0.287</v>
       </c>
-      <c r="T115" s="22" t="n">
+      <c r="T121" s="22" t="n">
         <v>522.59</v>
       </c>
-      <c r="U115" s="22" t="n">
+      <c r="U121" s="22" t="n">
         <v>-697.7910000000001</v>
       </c>
-      <c r="V115" s="22" t="n">
+      <c r="V121" s="22" t="n">
         <v>-840.002</v>
       </c>
-      <c r="W115" s="22" t="n">
+      <c r="W121" s="22" t="n">
         <v>49.592</v>
       </c>
-      <c r="X115" s="22" t="n">
+      <c r="X121" s="22" t="n">
         <v>30.288</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>기타포괄손익 합계</t>
         </is>
       </c>
-      <c r="C116" s="22" t="n">
+      <c r="C122" s="22" t="n">
         <v>449.733</v>
       </c>
-      <c r="D116" s="22" t="n">
+      <c r="D122" s="22" t="n">
         <v>-840.002</v>
       </c>
-      <c r="E116" s="22" t="n">
+      <c r="E122" s="22" t="n">
         <v>60.963</v>
       </c>
-      <c r="F116" s="22" t="n">
+      <c r="F122" s="22" t="n">
         <v>24.694</v>
       </c>
-      <c r="G116" s="22" t="n">
+      <c r="G122" s="22" t="n">
         <v>-68.005</v>
       </c>
-      <c r="H116" s="22" t="n">
+      <c r="H122" s="22" t="n">
         <v>49.592</v>
       </c>
-      <c r="I116" s="22" t="n">
+      <c r="I122" s="22" t="n">
         <v>-25.084</v>
       </c>
-      <c r="J116" s="22" t="n">
+      <c r="J122" s="22" t="n">
         <v>-16.655</v>
       </c>
-      <c r="K116" s="22" t="n">
+      <c r="K122" s="22" t="n">
         <v>54.819</v>
       </c>
-      <c r="L116" s="22" t="n">
+      <c r="L122" s="22" t="n">
         <v>30.288</v>
       </c>
-      <c r="M116" s="22" t="n">
+      <c r="M122" s="22" t="n">
         <v>7.724</v>
       </c>
-      <c r="N116" s="22" t="n">
+      <c r="N122" s="22" t="n">
         <v>-0.287</v>
       </c>
-      <c r="T116" s="22" t="n">
+      <c r="T122" s="22" t="n">
         <v>522.59</v>
       </c>
-      <c r="U116" s="22" t="n">
+      <c r="U122" s="22" t="n">
         <v>-697.7910000000001</v>
       </c>
-      <c r="V116" s="22" t="n">
+      <c r="V122" s="22" t="n">
         <v>-840.002</v>
       </c>
-      <c r="W116" s="22" t="n">
+      <c r="W122" s="22" t="n">
         <v>49.592</v>
       </c>
-      <c r="X116" s="22" t="n">
+      <c r="X122" s="22" t="n">
         <v>30.288</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>476.906</v>
-      </c>
-      <c r="D117" s="12" t="n">
-        <v>-13306.455</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>121.505</v>
-      </c>
-      <c r="F117" s="12" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="G117" s="12" t="n">
-        <v>20.866</v>
-      </c>
-      <c r="H117" s="12" t="n">
-        <v>330.628</v>
-      </c>
-      <c r="I117" s="12" t="n">
-        <v>56.612</v>
-      </c>
-      <c r="J117" s="12" t="n">
-        <v>83.297</v>
-      </c>
-      <c r="K117" s="12" t="n">
-        <v>376.406</v>
-      </c>
-      <c r="L117" s="12" t="n">
-        <v>418.955</v>
-      </c>
-      <c r="M117" s="12" t="n">
-        <v>234.136</v>
-      </c>
-      <c r="N117" s="12" t="n">
-        <v>262.351</v>
-      </c>
-      <c r="T117" s="12" t="n">
-        <v>588.277</v>
-      </c>
-      <c r="U117" s="12" t="n">
-        <v>-532.064</v>
-      </c>
-      <c r="V117" s="12" t="n">
-        <v>-13306.455</v>
-      </c>
-      <c r="W117" s="12" t="n">
-        <v>330.628</v>
-      </c>
-      <c r="X117" s="12" t="n">
-        <v>418.955</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n">
-        <v>476.906</v>
-      </c>
-      <c r="D118" s="12" t="n">
-        <v>-13306.455</v>
-      </c>
-      <c r="E118" s="12" t="n">
-        <v>121.505</v>
-      </c>
-      <c r="F118" s="12" t="n">
-        <v>71.48999999999999</v>
-      </c>
-      <c r="G118" s="12" t="n">
-        <v>20.866</v>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>330.628</v>
-      </c>
-      <c r="I118" s="12" t="n">
-        <v>56.612</v>
-      </c>
-      <c r="J118" s="12" t="n">
-        <v>83.297</v>
-      </c>
-      <c r="K118" s="12" t="n">
-        <v>376.406</v>
-      </c>
-      <c r="L118" s="12" t="n">
-        <v>418.955</v>
-      </c>
-      <c r="M118" s="12" t="n">
-        <v>234.136</v>
-      </c>
-      <c r="N118" s="12" t="n">
-        <v>262.351</v>
-      </c>
-      <c r="T118" s="12" t="n">
-        <v>588.277</v>
-      </c>
-      <c r="U118" s="12" t="n">
-        <v>-532.064</v>
-      </c>
-      <c r="V118" s="12" t="n">
-        <v>-13306.455</v>
-      </c>
-      <c r="W118" s="12" t="n">
-        <v>330.628</v>
-      </c>
-      <c r="X118" s="12" t="n">
-        <v>418.955</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>비지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B121" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C121" s="18" t="n"/>
-      <c r="D121" s="18" t="n"/>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
-      <c r="G121" s="18" t="n"/>
-      <c r="H121" s="18" t="n"/>
-      <c r="I121" s="18" t="n"/>
-      <c r="J121" s="18" t="n"/>
-      <c r="K121" s="18" t="n"/>
-      <c r="L121" s="18" t="n"/>
-      <c r="M121" s="18" t="n"/>
-      <c r="N121" s="18" t="n"/>
-      <c r="O121" s="18" t="n"/>
-      <c r="P121" s="18" t="n"/>
-      <c r="Q121" s="18" t="n"/>
-      <c r="R121" s="18" t="n"/>
-      <c r="S121" s="18" t="n"/>
-      <c r="T121" s="18" t="n"/>
-      <c r="U121" s="18" t="n"/>
-      <c r="V121" s="18" t="n"/>
-      <c r="W121" s="18" t="n"/>
-      <c r="X121" s="18" t="n"/>
-      <c r="Y121" s="18" t="n"/>
-      <c r="Z121" s="18" t="n"/>
-      <c r="AA121" s="18" t="n"/>
-      <c r="AB121" s="18" t="n"/>
-      <c r="AC121" s="18" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="H122" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="M122" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="N122" s="5" t="inlineStr">
-        <is>
-          <t>2027.2Q</t>
-        </is>
-      </c>
-      <c r="O122" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P122" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q122" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R122" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S122" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T122" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U122" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V122" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W122" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X122" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y122" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z122" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA122" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB122" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC122" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>476.906</v>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>-13306.455</v>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>121.505</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>20.866</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>330.628</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>56.612</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>83.297</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>376.406</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>418.955</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>234.136</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>262.351</v>
+      </c>
+      <c r="T123" s="12" t="n">
+        <v>588.277</v>
+      </c>
+      <c r="U123" s="12" t="n">
+        <v>-532.064</v>
+      </c>
+      <c r="V123" s="12" t="n">
+        <v>-13306.455</v>
+      </c>
+      <c r="W123" s="12" t="n">
+        <v>330.628</v>
+      </c>
+      <c r="X123" s="12" t="n">
+        <v>418.955</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>476.906</v>
+      </c>
+      <c r="D124" s="12" t="n">
+        <v>-13306.455</v>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>121.505</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>20.866</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>330.628</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>56.612</v>
+      </c>
+      <c r="J124" s="12" t="n">
+        <v>83.297</v>
+      </c>
+      <c r="K124" s="12" t="n">
+        <v>376.406</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>418.955</v>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>234.136</v>
+      </c>
+      <c r="N124" s="12" t="n">
+        <v>262.351</v>
+      </c>
+      <c r="T124" s="12" t="n">
+        <v>588.277</v>
+      </c>
+      <c r="U124" s="12" t="n">
+        <v>-532.064</v>
+      </c>
+      <c r="V124" s="12" t="n">
+        <v>-13306.455</v>
+      </c>
+      <c r="W124" s="12" t="n">
+        <v>330.628</v>
+      </c>
+      <c r="X124" s="12" t="n">
+        <v>418.955</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>비지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B127" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+      <c r="J127" s="18" t="n"/>
+      <c r="K127" s="18" t="n"/>
+      <c r="L127" s="18" t="n"/>
+      <c r="M127" s="18" t="n"/>
+      <c r="N127" s="18" t="n"/>
+      <c r="O127" s="18" t="n"/>
+      <c r="P127" s="18" t="n"/>
+      <c r="Q127" s="18" t="n"/>
+      <c r="R127" s="18" t="n"/>
+      <c r="S127" s="18" t="n"/>
+      <c r="T127" s="18" t="n"/>
+      <c r="U127" s="18" t="n"/>
+      <c r="V127" s="18" t="n"/>
+      <c r="W127" s="18" t="n"/>
+      <c r="X127" s="18" t="n"/>
+      <c r="Y127" s="18" t="n"/>
+      <c r="Z127" s="18" t="n"/>
+      <c r="AA127" s="18" t="n"/>
+      <c r="AB127" s="18" t="n"/>
+      <c r="AC127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>2027.2Q</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P128" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q128" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R128" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S128" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T128" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U128" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V128" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W128" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X128" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y128" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z128" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA128" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB128" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC128" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="D123" s="12" t="n">
+      <c r="D129" s="12" t="n">
         <v>-14392.986</v>
       </c>
-      <c r="F123" s="12" t="n">
+      <c r="F129" s="12" t="n">
         <v>305.112</v>
       </c>
-      <c r="H123" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>812.813</v>
       </c>
-      <c r="J123" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>366.169</v>
       </c>
-      <c r="L123" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>1149.747</v>
       </c>
-      <c r="N123" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>752.378</v>
       </c>
-      <c r="Q123" s="12" t="n">
+      <c r="Q129" s="12" t="n">
         <v>24.075</v>
       </c>
-      <c r="R123" s="12" t="n">
+      <c r="R129" s="12" t="n">
         <v>53.185</v>
       </c>
-      <c r="S123" s="12" t="n">
+      <c r="S129" s="12" t="n">
         <v>197.232</v>
       </c>
-      <c r="T123" s="12" t="n">
+      <c r="T129" s="12" t="n">
         <v>-389.762</v>
       </c>
-      <c r="U123" s="12" t="n">
+      <c r="U129" s="12" t="n">
         <v>-51.169</v>
       </c>
-      <c r="V123" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>-14392.986</v>
       </c>
-      <c r="W123" s="12" t="n">
+      <c r="W129" s="12" t="n">
         <v>812.813</v>
       </c>
-      <c r="X123" s="12" t="n">
+      <c r="X129" s="12" t="n">
         <v>1149.747</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="D124" s="22" t="n">
-        <v>818.6420000000001</v>
-      </c>
-      <c r="F124" s="22" t="n">
-        <v>10.283</v>
-      </c>
-      <c r="H124" s="22" t="n">
-        <v>53.268</v>
-      </c>
-      <c r="J124" s="22" t="n">
-        <v>18.278</v>
-      </c>
-      <c r="L124" s="22" t="n">
-        <v>51.865</v>
-      </c>
-      <c r="N124" s="22" t="n">
-        <v>28.375</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>9.319000000000001</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>15.612</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>18.301</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>165.84</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>708.246</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>818.6420000000001</v>
-      </c>
-      <c r="W124" s="22" t="n">
-        <v>53.268</v>
-      </c>
-      <c r="X124" s="22" t="n">
-        <v>51.865</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="D125" s="22" t="n">
-        <v>446.746</v>
-      </c>
-      <c r="F125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>90.352</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>417.728</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>446.746</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>상장 관련 비용</t>
-        </is>
-      </c>
-      <c r="S126" s="22" t="n">
-        <v>1.983</v>
-      </c>
-      <c r="T126" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>자금조달비용</t>
-        </is>
-      </c>
-      <c r="S127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" s="22" t="n">
-        <v>261.681</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>자금조달비용</t>
-        </is>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>261.681</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="D129" s="22" t="n">
-        <v>14472.936</v>
-      </c>
-      <c r="F129" s="22" t="n">
-        <v>263.453</v>
-      </c>
-      <c r="H129" s="22" t="n">
-        <v>398.955</v>
-      </c>
-      <c r="J129" s="22" t="n">
-        <v>137.195</v>
-      </c>
-      <c r="L129" s="22" t="n">
-        <v>254.135</v>
-      </c>
-      <c r="N129" s="22" t="n">
-        <v>128.029</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>14472.936</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>398.955</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>254.135</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>채무 환입이익</t>
-        </is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>818.6420000000001</v>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>10.283</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>0</v>
+        <v>53.268</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>18.278</v>
       </c>
       <c r="L130" s="22" t="n">
-        <v>-25.657</v>
+        <v>51.865</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>28.375</v>
+      </c>
+      <c r="Q130" s="22" t="n">
+        <v>9.319000000000001</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>15.612</v>
+      </c>
+      <c r="S130" s="22" t="n">
+        <v>18.301</v>
+      </c>
+      <c r="T130" s="22" t="n">
+        <v>165.84</v>
+      </c>
+      <c r="U130" s="22" t="n">
+        <v>708.246</v>
+      </c>
+      <c r="V130" s="22" t="n">
+        <v>818.6420000000001</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>0</v>
+        <v>53.268</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-25.657</v>
+        <v>51.865</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>-98.988</v>
+        <v>446.746</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>-2.581</v>
+        <v>0</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>-2.625</v>
-      </c>
-      <c r="J131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S131" s="22" t="n">
         <v>0</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>-2.675</v>
+        <v>90.352</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-5.154</v>
+        <v>417.728</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>-98.988</v>
+        <v>446.746</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-2.625</v>
-      </c>
-      <c r="X131" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>보험금 수익</t>
-        </is>
-      </c>
-      <c r="D132" s="22" t="n">
-        <v>-31.297</v>
-      </c>
-      <c r="H132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" s="22" t="n">
-        <v>-31.297</v>
-      </c>
-      <c r="W132" s="22" t="n">
+          <t>상장 관련 비용</t>
+        </is>
+      </c>
+      <c r="S132" s="22" t="n">
+        <v>1.983</v>
+      </c>
+      <c r="T132" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
-        </is>
-      </c>
-      <c r="D133" s="22" t="n">
-        <v>32.468</v>
-      </c>
-      <c r="H133" s="22" t="n">
+          <t>자금조달비용</t>
+        </is>
+      </c>
+      <c r="S133" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" s="22" t="n">
-        <v>32.468</v>
-      </c>
-      <c r="W133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" s="22" t="n">
-        <v>0</v>
+      <c r="T133" s="22" t="n">
+        <v>261.681</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>관계회사 청산손익</t>
-        </is>
-      </c>
-      <c r="J134" s="22" t="n">
+          <t>자금조달비용</t>
+        </is>
+      </c>
+      <c r="T134" s="22" t="n">
+        <v>261.681</v>
+      </c>
+      <c r="U134" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="N134" s="22" t="n">
-        <v>-29.919</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>79.145</v>
+        <v>14472.936</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>-97.925</v>
+        <v>263.453</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>33.868</v>
+        <v>398.955</v>
       </c>
       <c r="J135" s="22" t="n">
-        <v>-170.907</v>
+        <v>137.195</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>9.378</v>
+        <v>254.135</v>
       </c>
       <c r="N135" s="22" t="n">
-        <v>-121.936</v>
-      </c>
-      <c r="Q135" s="22" t="n">
+        <v>128.029</v>
+      </c>
+      <c r="U135" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R135" s="22" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="S135" s="22" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="T135" s="22" t="n">
-        <v>80.764</v>
-      </c>
-      <c r="U135" s="22" t="n">
-        <v>-91.827</v>
-      </c>
       <c r="V135" s="22" t="n">
-        <v>79.145</v>
+        <v>14472.936</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>33.868</v>
+        <v>398.955</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>9.378</v>
+        <v>254.135</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
-      </c>
-      <c r="Q136" s="22" t="n">
+          <t>채무 환입이익</t>
+        </is>
+      </c>
+      <c r="H136" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R136" s="22" t="n">
-        <v>10.842</v>
+      <c r="L136" s="22" t="n">
+        <v>-25.657</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>-25.657</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>자기 신주예약권</t>
-        </is>
-      </c>
-      <c r="Q137" s="22" t="n">
+          <t>보조금 수입</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>-98.988</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>-2.581</v>
+      </c>
+      <c r="H137" s="22" t="n">
+        <v>-2.625</v>
+      </c>
+      <c r="J137" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R137" s="22" t="n">
-        <v>4.067</v>
+      <c r="L137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="22" t="n">
+        <v>-2.675</v>
+      </c>
+      <c r="U137" s="22" t="n">
+        <v>-5.154</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>-98.988</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-2.625</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>대손충당금 증감</t>
+          <t>보험금 수익</t>
         </is>
       </c>
       <c r="D138" s="22" t="n">
-        <v>-2.624</v>
-      </c>
-      <c r="F138" s="22" t="n">
-        <v>-3.507</v>
+        <v>-31.297</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>-4.408</v>
-      </c>
-      <c r="J138" s="22" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="L138" s="22" t="n">
-        <v>3.654</v>
-      </c>
-      <c r="N138" s="22" t="n">
-        <v>-1.746</v>
-      </c>
-      <c r="S138" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="22" t="n">
-        <v>-17.183</v>
-      </c>
       <c r="U138" s="22" t="n">
-        <v>2.075</v>
+        <v>0</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>-2.624</v>
+        <v>-31.297</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>-4.408</v>
-      </c>
-      <c r="X138" s="22" t="n">
-        <v>3.654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
-        <v>-0.053</v>
-      </c>
-      <c r="F139" s="22" t="n">
-        <v>-0.133</v>
+        <v>32.468</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>-1.063</v>
-      </c>
-      <c r="J139" s="22" t="n">
-        <v>-2.925</v>
+        <v>0</v>
       </c>
       <c r="L139" s="22" t="n">
-        <v>-8.448</v>
-      </c>
-      <c r="N139" s="22" t="n">
-        <v>-7.598</v>
-      </c>
-      <c r="Q139" s="22" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="R139" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="S139" s="22" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="T139" s="22" t="n">
-        <v>-0.024</v>
+        <v>0</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>-0.027</v>
+        <v>0</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-0.053</v>
+        <v>32.468</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-1.063</v>
+        <v>0</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-8.448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="D140" s="22" t="n">
-        <v>37.127</v>
-      </c>
-      <c r="F140" s="22" t="n">
-        <v>19.813</v>
-      </c>
-      <c r="H140" s="22" t="n">
-        <v>43.668</v>
+          <t>관계회사 청산손익</t>
+        </is>
       </c>
       <c r="J140" s="22" t="n">
-        <v>27.545</v>
-      </c>
-      <c r="L140" s="22" t="n">
-        <v>52.982</v>
+        <v>0</v>
       </c>
       <c r="N140" s="22" t="n">
-        <v>25.459</v>
-      </c>
-      <c r="Q140" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>3.321</v>
-      </c>
-      <c r="S140" s="22" t="n">
-        <v>8.481</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>22.121</v>
-      </c>
-      <c r="U140" s="22" t="n">
-        <v>46.105</v>
-      </c>
-      <c r="V140" s="22" t="n">
-        <v>37.127</v>
-      </c>
-      <c r="W140" s="22" t="n">
-        <v>43.668</v>
-      </c>
-      <c r="X140" s="22" t="n">
-        <v>52.982</v>
+        <v>-29.919</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
+          <t>상여충당금 증감</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>79.145</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>-97.925</v>
+      </c>
+      <c r="H141" s="22" t="n">
+        <v>33.868</v>
+      </c>
+      <c r="J141" s="22" t="n">
+        <v>-170.907</v>
+      </c>
+      <c r="L141" s="22" t="n">
+        <v>9.378</v>
+      </c>
+      <c r="N141" s="22" t="n">
+        <v>-121.936</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>-0.136</v>
+        <v>0</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>0.148</v>
+        <v>9.49</v>
+      </c>
+      <c r="S141" s="22" t="n">
+        <v>51.95</v>
+      </c>
+      <c r="T141" s="22" t="n">
+        <v>80.764</v>
+      </c>
+      <c r="U141" s="22" t="n">
+        <v>-91.827</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>79.145</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>33.868</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>9.378</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>상장 관련 비용</t>
         </is>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>-71.636</v>
+        <v>0</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-51.53</v>
+        <v>10.842</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>자기 신주예약권</t>
         </is>
       </c>
       <c r="Q143" s="22" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="R143" s="22" t="n">
-        <v>0</v>
+        <v>4.067</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>장기선급비용 증감</t>
-        </is>
-      </c>
-      <c r="Q144" s="22" t="n">
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="n">
+        <v>-2.624</v>
+      </c>
+      <c r="F144" s="22" t="n">
+        <v>-3.507</v>
+      </c>
+      <c r="H144" s="22" t="n">
+        <v>-4.408</v>
+      </c>
+      <c r="J144" s="22" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="L144" s="22" t="n">
+        <v>3.654</v>
+      </c>
+      <c r="N144" s="22" t="n">
+        <v>-1.746</v>
+      </c>
+      <c r="S144" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R144" s="22" t="n">
-        <v>-0.468</v>
+      <c r="T144" s="22" t="n">
+        <v>-17.183</v>
+      </c>
+      <c r="U144" s="22" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="V144" s="22" t="n">
+        <v>-2.624</v>
+      </c>
+      <c r="W144" s="22" t="n">
+        <v>-4.408</v>
+      </c>
+      <c r="X144" s="22" t="n">
+        <v>3.654</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
-        </is>
+          <t>이자·배당금 수익</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="F145" s="22" t="n">
+        <v>-0.133</v>
+      </c>
+      <c r="H145" s="22" t="n">
+        <v>-1.063</v>
+      </c>
+      <c r="J145" s="22" t="n">
+        <v>-2.925</v>
+      </c>
+      <c r="L145" s="22" t="n">
+        <v>-8.448</v>
+      </c>
+      <c r="N145" s="22" t="n">
+        <v>-7.598</v>
       </c>
       <c r="Q145" s="22" t="n">
-        <v>-10.333</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>-10.189</v>
+        <v>-0.033</v>
+      </c>
+      <c r="S145" s="22" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="T145" s="22" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="U145" s="22" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="V145" s="22" t="n">
+        <v>-0.053</v>
+      </c>
+      <c r="W145" s="22" t="n">
+        <v>-1.063</v>
+      </c>
+      <c r="X145" s="22" t="n">
+        <v>-8.448</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>외환차손익</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="D146" s="22" t="n">
-        <v>-22.571</v>
+        <v>37.127</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>14.608</v>
+        <v>19.813</v>
       </c>
       <c r="H146" s="22" t="n">
-        <v>3.814</v>
+        <v>43.668</v>
       </c>
       <c r="J146" s="22" t="n">
-        <v>8.702999999999999</v>
+        <v>27.545</v>
       </c>
       <c r="L146" s="22" t="n">
-        <v>-3.916</v>
+        <v>52.982</v>
       </c>
       <c r="N146" s="22" t="n">
-        <v>10.245</v>
+        <v>25.459</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>3.321</v>
       </c>
       <c r="S146" s="22" t="n">
-        <v>2.404</v>
+        <v>8.481</v>
       </c>
       <c r="T146" s="22" t="n">
-        <v>-6.701</v>
+        <v>22.121</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>-14.892</v>
+        <v>46.105</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>-22.571</v>
+        <v>37.127</v>
       </c>
       <c r="W146" s="22" t="n">
-        <v>3.814</v>
+        <v>43.668</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-3.916</v>
+        <v>52.982</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="D147" s="22" t="n">
-        <v>-356.094</v>
-      </c>
-      <c r="U147" s="22" t="n">
-        <v>-18.266</v>
-      </c>
-      <c r="V147" s="22" t="n">
-        <v>-356.094</v>
+          <t>외환차손익</t>
+        </is>
+      </c>
+      <c r="Q147" s="22" t="n">
+        <v>-0.136</v>
+      </c>
+      <c r="R147" s="22" t="n">
+        <v>0.148</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>매출채권·계약자산 증감</t>
-        </is>
-      </c>
-      <c r="D148" s="22" t="n">
-        <v>-356.094</v>
-      </c>
-      <c r="H148" s="22" t="n">
-        <v>75.575</v>
-      </c>
-      <c r="L148" s="22" t="n">
-        <v>-4.856</v>
-      </c>
-      <c r="V148" s="22" t="n">
-        <v>-356.094</v>
-      </c>
-      <c r="W148" s="22" t="n">
-        <v>75.575</v>
-      </c>
-      <c r="X148" s="22" t="n">
-        <v>-4.856</v>
+          <t>매출채권 증감</t>
+        </is>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>-71.636</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>-51.53</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="F149" s="22" t="n">
-        <v>347.586</v>
-      </c>
-      <c r="J149" s="22" t="n">
-        <v>405.669</v>
-      </c>
-      <c r="N149" s="22" t="n">
-        <v>101.964</v>
-      </c>
-      <c r="S149" s="22" t="n">
-        <v>-209.498</v>
-      </c>
-      <c r="T149" s="22" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="U149" s="22" t="n">
-        <v>-18.266</v>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="Q149" s="22" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="R149" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="D150" s="22" t="n">
-        <v>44.536</v>
-      </c>
-      <c r="F150" s="22" t="n">
-        <v>-49.13</v>
-      </c>
-      <c r="H150" s="22" t="n">
-        <v>-18.118</v>
-      </c>
-      <c r="J150" s="22" t="n">
-        <v>-43.829</v>
-      </c>
-      <c r="L150" s="22" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="N150" s="22" t="n">
-        <v>-43.782</v>
+          <t>장기선급비용 증감</t>
+        </is>
       </c>
       <c r="Q150" s="22" t="n">
-        <v>22.81</v>
+        <v>0</v>
       </c>
       <c r="R150" s="22" t="n">
-        <v>17.536</v>
-      </c>
-      <c r="S150" s="22" t="n">
-        <v>50.441</v>
-      </c>
-      <c r="T150" s="22" t="n">
-        <v>78.676</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>26.419</v>
-      </c>
-      <c r="V150" s="22" t="n">
-        <v>44.536</v>
-      </c>
-      <c r="W150" s="22" t="n">
-        <v>-18.118</v>
-      </c>
-      <c r="X150" s="22" t="n">
-        <v>0.003</v>
+        <v>-0.468</v>
       </c>
     </row>
     <row r="151">
@@ -8862,1290 +9094,1281 @@
           <t>선급비용 증감</t>
         </is>
       </c>
-      <c r="D151" s="22" t="n">
-        <v>-36.455</v>
-      </c>
-      <c r="F151" s="22" t="n">
-        <v>9.500999999999999</v>
-      </c>
-      <c r="H151" s="22" t="n">
-        <v>-41.824</v>
-      </c>
-      <c r="J151" s="22" t="n">
-        <v>20.253</v>
-      </c>
-      <c r="L151" s="22" t="n">
-        <v>60.906</v>
-      </c>
-      <c r="N151" s="22" t="n">
-        <v>-64.654</v>
-      </c>
-      <c r="S151" s="22" t="n">
-        <v>5.518</v>
-      </c>
-      <c r="T151" s="22" t="n">
-        <v>-44.743</v>
-      </c>
-      <c r="U151" s="22" t="n">
-        <v>27.688</v>
-      </c>
-      <c r="V151" s="22" t="n">
-        <v>-36.455</v>
-      </c>
-      <c r="W151" s="22" t="n">
-        <v>-41.824</v>
-      </c>
-      <c r="X151" s="22" t="n">
-        <v>60.906</v>
+      <c r="Q151" s="22" t="n">
+        <v>-10.333</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>-10.189</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="D152" s="22" t="n">
-        <v>-12.55</v>
+        <v>-22.571</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>132.501</v>
+        <v>14.608</v>
       </c>
       <c r="H152" s="22" t="n">
-        <v>72.03400000000001</v>
+        <v>3.814</v>
       </c>
       <c r="J152" s="22" t="n">
-        <v>-60.976</v>
+        <v>8.702999999999999</v>
       </c>
       <c r="L152" s="22" t="n">
-        <v>3.678</v>
+        <v>-3.916</v>
       </c>
       <c r="N152" s="22" t="n">
-        <v>-79.102</v>
-      </c>
-      <c r="Q152" s="22" t="n">
-        <v>13.959</v>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>-0.518</v>
+        <v>10.245</v>
       </c>
       <c r="S152" s="22" t="n">
-        <v>24.942</v>
+        <v>2.404</v>
       </c>
       <c r="T152" s="22" t="n">
-        <v>-247.697</v>
+        <v>-6.701</v>
       </c>
       <c r="U152" s="22" t="n">
-        <v>-19.321</v>
+        <v>-14.892</v>
       </c>
       <c r="V152" s="22" t="n">
-        <v>-12.55</v>
+        <v>-22.571</v>
       </c>
       <c r="W152" s="22" t="n">
-        <v>72.03400000000001</v>
+        <v>3.814</v>
       </c>
       <c r="X152" s="22" t="n">
-        <v>3.678</v>
+        <v>-3.916</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>미지급비용 증감</t>
+          <t>매출채권·계약자산 증감</t>
         </is>
       </c>
       <c r="D153" s="22" t="n">
-        <v>28.528</v>
-      </c>
-      <c r="F153" s="22" t="n">
-        <v>22.126</v>
-      </c>
-      <c r="H153" s="22" t="n">
-        <v>-20.196</v>
-      </c>
-      <c r="J153" s="22" t="n">
-        <v>46.039</v>
-      </c>
-      <c r="L153" s="22" t="n">
-        <v>-0.429</v>
-      </c>
-      <c r="N153" s="22" t="n">
-        <v>-10.006</v>
-      </c>
-      <c r="Q153" s="22" t="n">
-        <v>2.224</v>
-      </c>
-      <c r="R153" s="22" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="S153" s="22" t="n">
-        <v>1.764</v>
-      </c>
-      <c r="T153" s="22" t="n">
-        <v>-16.279</v>
+        <v>-356.094</v>
       </c>
       <c r="U153" s="22" t="n">
-        <v>31.288</v>
+        <v>-18.266</v>
       </c>
       <c r="V153" s="22" t="n">
-        <v>28.528</v>
-      </c>
-      <c r="W153" s="22" t="n">
-        <v>-20.196</v>
-      </c>
-      <c r="X153" s="22" t="n">
-        <v>-0.429</v>
+        <v>-356.094</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
-      </c>
-      <c r="Q154" s="22" t="n">
-        <v>46.569</v>
-      </c>
-      <c r="R154" s="22" t="n">
-        <v>50.619</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>193.25</v>
-      </c>
-      <c r="T154" s="22" t="n">
-        <v>353.998</v>
-      </c>
-      <c r="U154" s="22" t="n">
-        <v>376.924</v>
+          <t>매출채권·계약자산 증감</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>-356.094</v>
+      </c>
+      <c r="H154" s="22" t="n">
+        <v>75.575</v>
+      </c>
+      <c r="L154" s="22" t="n">
+        <v>-4.856</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>-356.094</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>75.575</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>-4.856</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
-        </is>
-      </c>
-      <c r="D155" s="22" t="n">
-        <v>373.773</v>
+          <t>매출채권 증감</t>
+        </is>
       </c>
       <c r="F155" s="22" t="n">
-        <v>-509.775</v>
+        <v>347.586</v>
+      </c>
+      <c r="J155" s="22" t="n">
+        <v>405.669</v>
+      </c>
+      <c r="N155" s="22" t="n">
+        <v>101.964</v>
+      </c>
+      <c r="S155" s="22" t="n">
+        <v>-209.498</v>
+      </c>
+      <c r="T155" s="22" t="n">
+        <v>51.85</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>376.924</v>
-      </c>
-      <c r="V155" s="22" t="n">
-        <v>373.773</v>
+        <v>-18.266</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="D156" s="22" t="n">
-        <v>373.773</v>
+        <v>44.536</v>
       </c>
       <c r="F156" s="22" t="n">
-        <v>-509.775</v>
+        <v>-49.13</v>
       </c>
       <c r="H156" s="22" t="n">
-        <v>-133.716</v>
+        <v>-18.118</v>
       </c>
       <c r="J156" s="22" t="n">
-        <v>-315.48</v>
+        <v>-43.829</v>
       </c>
       <c r="L156" s="22" t="n">
-        <v>-56.611</v>
+        <v>0.003</v>
       </c>
       <c r="N156" s="22" t="n">
-        <v>12.172</v>
+        <v>-43.782</v>
+      </c>
+      <c r="Q156" s="22" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="R156" s="22" t="n">
+        <v>17.536</v>
+      </c>
+      <c r="S156" s="22" t="n">
+        <v>50.441</v>
+      </c>
+      <c r="T156" s="22" t="n">
+        <v>78.676</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>26.419</v>
       </c>
       <c r="V156" s="22" t="n">
-        <v>373.773</v>
+        <v>44.536</v>
       </c>
       <c r="W156" s="22" t="n">
-        <v>-133.716</v>
+        <v>-18.118</v>
       </c>
       <c r="X156" s="22" t="n">
-        <v>-56.611</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>선수수익 증감</t>
+          <t>선급비용 증감</t>
         </is>
       </c>
       <c r="D157" s="22" t="n">
-        <v>1.319</v>
+        <v>-36.455</v>
       </c>
       <c r="F157" s="22" t="n">
-        <v>-0.109</v>
+        <v>9.500999999999999</v>
       </c>
       <c r="H157" s="22" t="n">
-        <v>0.972</v>
+        <v>-41.824</v>
       </c>
       <c r="J157" s="22" t="n">
-        <v>-1.286</v>
+        <v>20.253</v>
       </c>
       <c r="L157" s="22" t="n">
-        <v>45.408</v>
+        <v>60.906</v>
       </c>
       <c r="N157" s="22" t="n">
-        <v>-4.147</v>
-      </c>
-      <c r="Q157" s="22" t="n">
-        <v>2.226</v>
-      </c>
-      <c r="R157" s="22" t="n">
-        <v>0.206</v>
+        <v>-64.654</v>
       </c>
       <c r="S157" s="22" t="n">
-        <v>0.52</v>
+        <v>5.518</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-44.743</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>2.121</v>
+        <v>27.688</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>1.319</v>
+        <v>-36.455</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>0.972</v>
+        <v>-41.824</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>45.408</v>
+        <v>60.906</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="D158" s="22" t="n">
-        <v>33.833</v>
+        <v>-12.55</v>
       </c>
       <c r="F158" s="22" t="n">
-        <v>22.434</v>
+        <v>132.501</v>
       </c>
       <c r="H158" s="22" t="n">
-        <v>9.644</v>
+        <v>72.03400000000001</v>
       </c>
       <c r="J158" s="22" t="n">
-        <v>11.411</v>
+        <v>-60.976</v>
       </c>
       <c r="L158" s="22" t="n">
-        <v>-10.58</v>
+        <v>3.678</v>
       </c>
       <c r="N158" s="22" t="n">
-        <v>-10.234</v>
+        <v>-79.102</v>
       </c>
       <c r="Q158" s="22" t="n">
-        <v>2.901</v>
+        <v>13.959</v>
       </c>
       <c r="R158" s="22" t="n">
-        <v>10.248</v>
+        <v>-0.518</v>
       </c>
       <c r="S158" s="22" t="n">
-        <v>5.766</v>
+        <v>24.942</v>
       </c>
       <c r="T158" s="22" t="n">
-        <v>-1.835</v>
+        <v>-247.697</v>
       </c>
       <c r="U158" s="22" t="n">
-        <v>3.758</v>
+        <v>-19.321</v>
       </c>
       <c r="V158" s="22" t="n">
-        <v>33.833</v>
+        <v>-12.55</v>
       </c>
       <c r="W158" s="22" t="n">
-        <v>9.644</v>
+        <v>72.03400000000001</v>
       </c>
       <c r="X158" s="22" t="n">
-        <v>-10.58</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
+          <t>미지급비용 증감</t>
         </is>
       </c>
       <c r="D159" s="22" t="n">
-        <v>-41.174</v>
+        <v>28.528</v>
       </c>
       <c r="F159" s="22" t="n">
-        <v>-24.74</v>
+        <v>22.126</v>
       </c>
       <c r="H159" s="22" t="n">
-        <v>-20.715</v>
+        <v>-20.196</v>
       </c>
       <c r="J159" s="22" t="n">
-        <v>-56.513</v>
+        <v>46.039</v>
       </c>
       <c r="L159" s="22" t="n">
-        <v>33.05</v>
+        <v>-0.429</v>
       </c>
       <c r="N159" s="22" t="n">
-        <v>-20.796</v>
+        <v>-10.006</v>
       </c>
       <c r="Q159" s="22" t="n">
-        <v>6.27</v>
+        <v>2.224</v>
       </c>
       <c r="R159" s="22" t="n">
-        <v>19.157</v>
+        <v>16.28</v>
       </c>
       <c r="S159" s="22" t="n">
-        <v>36.354</v>
+        <v>1.764</v>
       </c>
       <c r="T159" s="22" t="n">
-        <v>-53.846</v>
+        <v>-16.279</v>
       </c>
       <c r="U159" s="22" t="n">
-        <v>164.504</v>
+        <v>31.288</v>
       </c>
       <c r="V159" s="22" t="n">
-        <v>-41.174</v>
+        <v>28.528</v>
       </c>
       <c r="W159" s="22" t="n">
-        <v>-20.715</v>
+        <v>-20.196</v>
       </c>
       <c r="X159" s="22" t="n">
-        <v>33.05</v>
+        <v>-0.429</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="Q160" s="22" t="n">
-        <v>-1.719</v>
+        <v>46.569</v>
       </c>
       <c r="R160" s="22" t="n">
-        <v>-2.916</v>
+        <v>50.619</v>
+      </c>
+      <c r="S160" s="22" t="n">
+        <v>193.25</v>
+      </c>
+      <c r="T160" s="22" t="n">
+        <v>353.998</v>
+      </c>
+      <c r="U160" s="22" t="n">
+        <v>376.924</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="20" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
-        </is>
-      </c>
-      <c r="Q161" s="22" t="n">
-        <v>3.038</v>
-      </c>
-      <c r="R161" s="22" t="n">
-        <v>-3.035</v>
+          <t>계약부채 증감</t>
+        </is>
+      </c>
+      <c r="D161" s="22" t="n">
+        <v>373.773</v>
+      </c>
+      <c r="F161" s="22" t="n">
+        <v>-509.775</v>
+      </c>
+      <c r="U161" s="22" t="n">
+        <v>376.924</v>
+      </c>
+      <c r="V161" s="22" t="n">
+        <v>373.773</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="D162" s="22" t="n">
-        <v>-64.514</v>
+        <v>373.773</v>
       </c>
       <c r="F162" s="22" t="n">
-        <v>-86.66800000000001</v>
+        <v>-509.775</v>
       </c>
       <c r="H162" s="22" t="n">
-        <v>-84.121</v>
+        <v>-133.716</v>
       </c>
       <c r="J162" s="22" t="n">
-        <v>-2.644</v>
+        <v>-315.48</v>
       </c>
       <c r="L162" s="22" t="n">
-        <v>-40.08</v>
+        <v>-56.611</v>
       </c>
       <c r="N162" s="22" t="n">
-        <v>-18.88</v>
-      </c>
-      <c r="S162" s="22" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="T162" s="22" t="n">
-        <v>-8.317</v>
-      </c>
-      <c r="U162" s="22" t="n">
-        <v>16.122</v>
+        <v>12.172</v>
       </c>
       <c r="V162" s="22" t="n">
-        <v>-64.514</v>
+        <v>373.773</v>
       </c>
       <c r="W162" s="22" t="n">
-        <v>-84.121</v>
+        <v>-133.716</v>
       </c>
       <c r="X162" s="22" t="n">
-        <v>-40.08</v>
+        <v>-56.611</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>선수수익 증감</t>
         </is>
       </c>
       <c r="D163" s="22" t="n">
-        <v>1309.747</v>
+        <v>1.319</v>
       </c>
       <c r="F163" s="22" t="n">
-        <v>372.851</v>
+        <v>-0.109</v>
       </c>
       <c r="H163" s="22" t="n">
-        <v>1177.822</v>
+        <v>0.972</v>
       </c>
       <c r="J163" s="22" t="n">
-        <v>390.021</v>
+        <v>-1.286</v>
       </c>
       <c r="L163" s="22" t="n">
-        <v>1514.23</v>
+        <v>45.408</v>
       </c>
       <c r="N163" s="22" t="n">
-        <v>645.818</v>
+        <v>-4.147</v>
       </c>
       <c r="Q163" s="22" t="n">
-        <v>51.272</v>
+        <v>2.226</v>
       </c>
       <c r="R163" s="22" t="n">
-        <v>142.025</v>
+        <v>0.206</v>
       </c>
       <c r="S163" s="22" t="n">
-        <v>401.766</v>
+        <v>0.52</v>
       </c>
       <c r="T163" s="22" t="n">
-        <v>315.658</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="U163" s="22" t="n">
-        <v>1622.326</v>
+        <v>2.121</v>
       </c>
       <c r="V163" s="22" t="n">
-        <v>1309.747</v>
+        <v>1.319</v>
       </c>
       <c r="W163" s="22" t="n">
-        <v>1177.822</v>
+        <v>0.972</v>
       </c>
       <c r="X163" s="22" t="n">
-        <v>1514.23</v>
+        <v>45.408</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>예수금 증감</t>
         </is>
       </c>
       <c r="D164" s="22" t="n">
-        <v>0.053</v>
+        <v>33.833</v>
       </c>
       <c r="F164" s="22" t="n">
-        <v>0.133</v>
+        <v>22.434</v>
       </c>
       <c r="H164" s="22" t="n">
-        <v>1.063</v>
+        <v>9.644</v>
       </c>
       <c r="J164" s="22" t="n">
-        <v>2.925</v>
+        <v>11.411</v>
       </c>
       <c r="L164" s="22" t="n">
-        <v>8.448</v>
+        <v>-10.58</v>
       </c>
       <c r="N164" s="22" t="n">
-        <v>7.598</v>
+        <v>-10.234</v>
       </c>
       <c r="Q164" s="22" t="n">
-        <v>0.008999999999999999</v>
+        <v>2.901</v>
       </c>
       <c r="R164" s="22" t="n">
-        <v>0.033</v>
+        <v>10.248</v>
       </c>
       <c r="S164" s="22" t="n">
-        <v>0.017</v>
+        <v>5.766</v>
       </c>
       <c r="T164" s="22" t="n">
-        <v>0.024</v>
+        <v>-1.835</v>
       </c>
       <c r="U164" s="22" t="n">
-        <v>0.027</v>
+        <v>3.758</v>
       </c>
       <c r="V164" s="22" t="n">
-        <v>0.053</v>
+        <v>33.833</v>
       </c>
       <c r="W164" s="22" t="n">
-        <v>1.063</v>
+        <v>9.644</v>
       </c>
       <c r="X164" s="22" t="n">
-        <v>8.448</v>
+        <v>-10.58</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="D165" s="22" t="n">
-        <v>-37.317</v>
+        <v>-41.174</v>
       </c>
       <c r="F165" s="22" t="n">
-        <v>-20.922</v>
+        <v>-24.74</v>
       </c>
       <c r="H165" s="22" t="n">
-        <v>-47.153</v>
+        <v>-20.715</v>
       </c>
       <c r="J165" s="22" t="n">
-        <v>-26.787</v>
+        <v>-56.513</v>
       </c>
       <c r="L165" s="22" t="n">
-        <v>-52.844</v>
+        <v>33.05</v>
       </c>
       <c r="N165" s="22" t="n">
-        <v>-18.369</v>
+        <v>-20.796</v>
       </c>
       <c r="Q165" s="22" t="n">
-        <v>-1.519</v>
+        <v>6.27</v>
       </c>
       <c r="R165" s="22" t="n">
-        <v>-3.338</v>
+        <v>19.157</v>
       </c>
       <c r="S165" s="22" t="n">
-        <v>-8.467000000000001</v>
+        <v>36.354</v>
       </c>
       <c r="T165" s="22" t="n">
-        <v>-25.235</v>
+        <v>-53.846</v>
       </c>
       <c r="U165" s="22" t="n">
-        <v>-45.054</v>
+        <v>164.504</v>
       </c>
       <c r="V165" s="22" t="n">
-        <v>-37.317</v>
+        <v>-41.174</v>
       </c>
       <c r="W165" s="22" t="n">
-        <v>-47.153</v>
+        <v>-20.715</v>
       </c>
       <c r="X165" s="22" t="n">
-        <v>-52.844</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="Q166" s="22" t="n">
-        <v>-3.082</v>
+        <v>-1.719</v>
       </c>
       <c r="R166" s="22" t="n">
-        <v>0.791</v>
+        <v>-2.916</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
-        </is>
-      </c>
-      <c r="D167" s="22" t="n">
-        <v>98.988</v>
-      </c>
-      <c r="F167" s="22" t="n">
-        <v>2.581</v>
-      </c>
-      <c r="H167" s="22" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="J167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" s="22" t="n">
-        <v>2.675</v>
-      </c>
-      <c r="U167" s="22" t="n">
-        <v>5.154</v>
-      </c>
-      <c r="V167" s="22" t="n">
-        <v>98.988</v>
-      </c>
-      <c r="W167" s="22" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="X167" s="22" t="n">
-        <v>0</v>
+          <t>기타 부채 증감</t>
+        </is>
+      </c>
+      <c r="Q167" s="22" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="R167" s="22" t="n">
+        <v>-3.035</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D168" s="22" t="n">
-        <v>31.297</v>
+        <v>-64.514</v>
+      </c>
+      <c r="F168" s="22" t="n">
+        <v>-86.66800000000001</v>
       </c>
       <c r="H168" s="22" t="n">
-        <v>0</v>
+        <v>-84.121</v>
+      </c>
+      <c r="J168" s="22" t="n">
+        <v>-2.644</v>
+      </c>
+      <c r="L168" s="22" t="n">
+        <v>-40.08</v>
+      </c>
+      <c r="N168" s="22" t="n">
+        <v>-18.88</v>
+      </c>
+      <c r="S168" s="22" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="T168" s="22" t="n">
+        <v>-8.317</v>
       </c>
       <c r="U168" s="22" t="n">
-        <v>0</v>
+        <v>16.122</v>
       </c>
       <c r="V168" s="22" t="n">
-        <v>31.297</v>
+        <v>-64.514</v>
       </c>
       <c r="W168" s="22" t="n">
-        <v>0</v>
+        <v>-84.121</v>
+      </c>
+      <c r="X168" s="22" t="n">
+        <v>-40.08</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="D169" s="22" t="n">
-        <v>-470.023</v>
+        <v>1309.747</v>
       </c>
       <c r="F169" s="22" t="n">
-        <v>-217.257</v>
+        <v>372.851</v>
       </c>
       <c r="H169" s="22" t="n">
-        <v>-389.152</v>
+        <v>1177.822</v>
       </c>
       <c r="J169" s="22" t="n">
-        <v>-141.533</v>
+        <v>390.021</v>
       </c>
       <c r="L169" s="22" t="n">
-        <v>-177.806</v>
+        <v>1514.23</v>
       </c>
       <c r="N169" s="22" t="n">
-        <v>-232.689</v>
+        <v>645.818</v>
+      </c>
+      <c r="Q169" s="22" t="n">
+        <v>51.272</v>
+      </c>
+      <c r="R169" s="22" t="n">
+        <v>142.025</v>
       </c>
       <c r="S169" s="22" t="n">
-        <v>-0.2</v>
+        <v>401.766</v>
       </c>
       <c r="T169" s="22" t="n">
-        <v>-62.153</v>
+        <v>315.658</v>
       </c>
       <c r="U169" s="22" t="n">
-        <v>-63.788</v>
+        <v>1622.326</v>
       </c>
       <c r="V169" s="22" t="n">
-        <v>-470.023</v>
+        <v>1309.747</v>
       </c>
       <c r="W169" s="22" t="n">
-        <v>-389.152</v>
+        <v>1177.822</v>
       </c>
       <c r="X169" s="22" t="n">
-        <v>-177.806</v>
+        <v>1514.23</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="D170" s="22" t="n">
-        <v>0</v>
+        <v>0.053</v>
+      </c>
+      <c r="F170" s="22" t="n">
+        <v>0.133</v>
       </c>
       <c r="H170" s="22" t="n">
-        <v>182.514</v>
+        <v>1.063</v>
+      </c>
+      <c r="J170" s="22" t="n">
+        <v>2.925</v>
       </c>
       <c r="L170" s="22" t="n">
-        <v>0</v>
+        <v>8.448</v>
+      </c>
+      <c r="N170" s="22" t="n">
+        <v>7.598</v>
+      </c>
+      <c r="Q170" s="22" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R170" s="22" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="S170" s="22" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="T170" s="22" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="U170" s="22" t="n">
+        <v>0.027</v>
       </c>
       <c r="V170" s="22" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="W170" s="22" t="n">
-        <v>182.514</v>
+        <v>1.063</v>
       </c>
       <c r="X170" s="22" t="n">
-        <v>0</v>
+        <v>8.448</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D171" s="12" t="n">
-        <v>932.746</v>
-      </c>
-      <c r="F171" s="12" t="n">
-        <v>137.386</v>
-      </c>
-      <c r="H171" s="12" t="n">
-        <v>927.72</v>
-      </c>
-      <c r="J171" s="12" t="n">
-        <v>224.625</v>
-      </c>
-      <c r="L171" s="12" t="n">
-        <v>1292.027</v>
-      </c>
-      <c r="N171" s="12" t="n">
-        <v>402.357</v>
-      </c>
-      <c r="Q171" s="12" t="n">
-        <v>46.678</v>
-      </c>
-      <c r="R171" s="12" t="n">
-        <v>139.511</v>
-      </c>
-      <c r="S171" s="12" t="n">
-        <v>393.115</v>
-      </c>
-      <c r="T171" s="12" t="n">
-        <v>230.97</v>
-      </c>
-      <c r="U171" s="12" t="n">
-        <v>1518.665</v>
-      </c>
-      <c r="V171" s="12" t="n">
-        <v>932.746</v>
-      </c>
-      <c r="W171" s="12" t="n">
-        <v>927.72</v>
-      </c>
-      <c r="X171" s="12" t="n">
-        <v>1292.027</v>
+      <c r="A171" s="20" t="inlineStr">
+        <is>
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="D171" s="22" t="n">
+        <v>-37.317</v>
+      </c>
+      <c r="F171" s="22" t="n">
+        <v>-20.922</v>
+      </c>
+      <c r="H171" s="22" t="n">
+        <v>-47.153</v>
+      </c>
+      <c r="J171" s="22" t="n">
+        <v>-26.787</v>
+      </c>
+      <c r="L171" s="22" t="n">
+        <v>-52.844</v>
+      </c>
+      <c r="N171" s="22" t="n">
+        <v>-18.369</v>
+      </c>
+      <c r="Q171" s="22" t="n">
+        <v>-1.519</v>
+      </c>
+      <c r="R171" s="22" t="n">
+        <v>-3.338</v>
+      </c>
+      <c r="S171" s="22" t="n">
+        <v>-8.467000000000001</v>
+      </c>
+      <c r="T171" s="22" t="n">
+        <v>-25.235</v>
+      </c>
+      <c r="U171" s="22" t="n">
+        <v>-45.054</v>
+      </c>
+      <c r="V171" s="22" t="n">
+        <v>-37.317</v>
+      </c>
+      <c r="W171" s="22" t="n">
+        <v>-47.153</v>
+      </c>
+      <c r="X171" s="22" t="n">
+        <v>-52.844</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
-        </is>
-      </c>
-      <c r="D172" s="22" t="n">
-        <v>-58.594</v>
-      </c>
-      <c r="F172" s="22" t="n">
-        <v>-18.182</v>
-      </c>
-      <c r="H172" s="22" t="n">
-        <v>-38.608</v>
-      </c>
-      <c r="J172" s="22" t="n">
-        <v>-114.454</v>
-      </c>
-      <c r="L172" s="22" t="n">
-        <v>-132.689</v>
-      </c>
-      <c r="N172" s="22" t="n">
-        <v>-44.176</v>
+          <t>법인세 납부·환급</t>
+        </is>
       </c>
       <c r="Q172" s="22" t="n">
-        <v>-22.527</v>
+        <v>-3.082</v>
       </c>
       <c r="R172" s="22" t="n">
-        <v>-10.646</v>
-      </c>
-      <c r="S172" s="22" t="n">
-        <v>-27.557</v>
-      </c>
-      <c r="T172" s="22" t="n">
-        <v>-26.037</v>
-      </c>
-      <c r="U172" s="22" t="n">
-        <v>-43.004</v>
-      </c>
-      <c r="V172" s="22" t="n">
-        <v>-58.594</v>
-      </c>
-      <c r="W172" s="22" t="n">
-        <v>-38.608</v>
-      </c>
-      <c r="X172" s="22" t="n">
-        <v>-132.689</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="D173" s="22" t="n">
-        <v>2.451</v>
+        <v>98.988</v>
+      </c>
+      <c r="F173" s="22" t="n">
+        <v>2.581</v>
       </c>
       <c r="H173" s="22" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="J173" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="L173" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="S173" s="22" t="n">
-        <v>0.394</v>
+        <v>0</v>
       </c>
       <c r="T173" s="22" t="n">
-        <v>0.291</v>
+        <v>2.675</v>
       </c>
       <c r="U173" s="22" t="n">
-        <v>0</v>
+        <v>5.154</v>
       </c>
       <c r="V173" s="22" t="n">
-        <v>2.451</v>
+        <v>98.988</v>
       </c>
       <c r="W173" s="22" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="X173" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="D174" s="22" t="n">
-        <v>-217.428</v>
-      </c>
-      <c r="F174" s="22" t="n">
-        <v>-125.409</v>
+        <v>31.297</v>
       </c>
       <c r="H174" s="22" t="n">
-        <v>-251.792</v>
-      </c>
-      <c r="J174" s="22" t="n">
-        <v>-130.935</v>
-      </c>
-      <c r="L174" s="22" t="n">
-        <v>-237.708</v>
-      </c>
-      <c r="N174" s="22" t="n">
-        <v>-123.094</v>
-      </c>
-      <c r="S174" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T174" s="22" t="n">
-        <v>-53.412</v>
-      </c>
       <c r="U174" s="22" t="n">
-        <v>-194.852</v>
+        <v>0</v>
       </c>
       <c r="V174" s="22" t="n">
-        <v>-217.428</v>
+        <v>31.297</v>
       </c>
       <c r="W174" s="22" t="n">
-        <v>-251.792</v>
-      </c>
-      <c r="X174" s="22" t="n">
-        <v>-237.708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 납입</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="D175" s="22" t="n">
-        <v>-13.739</v>
+        <v>-470.023</v>
       </c>
       <c r="F175" s="22" t="n">
-        <v>-1.423</v>
+        <v>-217.257</v>
       </c>
       <c r="H175" s="22" t="n">
-        <v>-4.632</v>
+        <v>-389.152</v>
       </c>
       <c r="J175" s="22" t="n">
-        <v>-19.884</v>
+        <v>-141.533</v>
       </c>
       <c r="L175" s="22" t="n">
-        <v>-22.649</v>
+        <v>-177.806</v>
       </c>
       <c r="N175" s="22" t="n">
-        <v>-5.177</v>
-      </c>
-      <c r="Q175" s="22" t="n">
-        <v>-24.73</v>
-      </c>
-      <c r="R175" s="22" t="n">
-        <v>-23.44</v>
+        <v>-232.689</v>
       </c>
       <c r="S175" s="22" t="n">
-        <v>-1.347</v>
+        <v>-0.2</v>
       </c>
       <c r="T175" s="22" t="n">
-        <v>-4.646</v>
+        <v>-62.153</v>
       </c>
       <c r="U175" s="22" t="n">
-        <v>-4.375</v>
+        <v>-63.788</v>
       </c>
       <c r="V175" s="22" t="n">
-        <v>-13.739</v>
+        <v>-470.023</v>
       </c>
       <c r="W175" s="22" t="n">
-        <v>-4.632</v>
+        <v>-389.152</v>
       </c>
       <c r="X175" s="22" t="n">
-        <v>-22.649</v>
+        <v>-177.806</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각</t>
-        </is>
-      </c>
-      <c r="Q176" s="22" t="n">
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R176" s="22" t="n">
-        <v>0.131</v>
+      <c r="H176" s="22" t="n">
+        <v>182.514</v>
+      </c>
+      <c r="L176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" s="22" t="n">
+        <v>182.514</v>
+      </c>
+      <c r="X176" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="20" t="inlineStr">
-        <is>
-          <t>임차보증금·보증금 회수</t>
-        </is>
-      </c>
-      <c r="D177" s="22" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="F177" s="22" t="n">
-        <v>19.052</v>
-      </c>
-      <c r="H177" s="22" t="n">
-        <v>25.204</v>
-      </c>
-      <c r="J177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L177" s="22" t="n">
-        <v>10.056</v>
-      </c>
-      <c r="N177" s="22" t="n">
-        <v>3.319</v>
-      </c>
-      <c r="S177" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" s="22" t="n">
-        <v>3.347</v>
-      </c>
-      <c r="U177" s="22" t="n">
-        <v>6.142</v>
-      </c>
-      <c r="V177" s="22" t="n">
-        <v>1.708</v>
-      </c>
-      <c r="W177" s="22" t="n">
-        <v>25.204</v>
-      </c>
-      <c r="X177" s="22" t="n">
-        <v>10.056</v>
+      <c r="A177" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D177" s="12" t="n">
+        <v>932.746</v>
+      </c>
+      <c r="F177" s="12" t="n">
+        <v>137.386</v>
+      </c>
+      <c r="H177" s="12" t="n">
+        <v>927.72</v>
+      </c>
+      <c r="J177" s="12" t="n">
+        <v>224.625</v>
+      </c>
+      <c r="L177" s="12" t="n">
+        <v>1292.027</v>
+      </c>
+      <c r="N177" s="12" t="n">
+        <v>402.357</v>
+      </c>
+      <c r="Q177" s="12" t="n">
+        <v>46.678</v>
+      </c>
+      <c r="R177" s="12" t="n">
+        <v>139.511</v>
+      </c>
+      <c r="S177" s="12" t="n">
+        <v>393.115</v>
+      </c>
+      <c r="T177" s="12" t="n">
+        <v>230.97</v>
+      </c>
+      <c r="U177" s="12" t="n">
+        <v>1518.665</v>
+      </c>
+      <c r="V177" s="12" t="n">
+        <v>932.746</v>
+      </c>
+      <c r="W177" s="12" t="n">
+        <v>927.72</v>
+      </c>
+      <c r="X177" s="12" t="n">
+        <v>1292.027</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="20" t="inlineStr">
         <is>
-          <t>장기투자 지출</t>
-        </is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="n">
+        <v>-58.594</v>
+      </c>
+      <c r="F178" s="22" t="n">
+        <v>-18.182</v>
+      </c>
+      <c r="H178" s="22" t="n">
+        <v>-38.608</v>
+      </c>
+      <c r="J178" s="22" t="n">
+        <v>-114.454</v>
+      </c>
+      <c r="L178" s="22" t="n">
+        <v>-132.689</v>
+      </c>
+      <c r="N178" s="22" t="n">
+        <v>-44.176</v>
+      </c>
+      <c r="Q178" s="22" t="n">
+        <v>-22.527</v>
+      </c>
+      <c r="R178" s="22" t="n">
+        <v>-10.646</v>
       </c>
       <c r="S178" s="22" t="n">
-        <v>-32.468</v>
+        <v>-27.557</v>
       </c>
       <c r="T178" s="22" t="n">
-        <v>0</v>
+        <v>-26.037</v>
+      </c>
+      <c r="U178" s="22" t="n">
+        <v>-43.004</v>
+      </c>
+      <c r="V178" s="22" t="n">
+        <v>-58.594</v>
+      </c>
+      <c r="W178" s="22" t="n">
+        <v>-38.608</v>
+      </c>
+      <c r="X178" s="22" t="n">
+        <v>-132.689</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="20" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="D179" s="22" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="H179" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S179" s="22" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="T179" s="22" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="U179" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T179" s="22" t="n">
-        <v>-11042.562</v>
-      </c>
-      <c r="U179" s="22" t="n">
-        <v>-197.837</v>
-      </c>
       <c r="V179" s="22" t="n">
+        <v>2.451</v>
+      </c>
+      <c r="W179" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="20" t="inlineStr">
         <is>
-          <t>대여</t>
-        </is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="n">
+        <v>-217.428</v>
+      </c>
+      <c r="F180" s="22" t="n">
+        <v>-125.409</v>
+      </c>
+      <c r="H180" s="22" t="n">
+        <v>-251.792</v>
       </c>
       <c r="J180" s="22" t="n">
+        <v>-130.935</v>
+      </c>
+      <c r="L180" s="22" t="n">
+        <v>-237.708</v>
+      </c>
+      <c r="N180" s="22" t="n">
+        <v>-123.094</v>
+      </c>
+      <c r="S180" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N180" s="22" t="n">
-        <v>-95</v>
+      <c r="T180" s="22" t="n">
+        <v>-53.412</v>
+      </c>
+      <c r="U180" s="22" t="n">
+        <v>-194.852</v>
+      </c>
+      <c r="V180" s="22" t="n">
+        <v>-217.428</v>
+      </c>
+      <c r="W180" s="22" t="n">
+        <v>-251.792</v>
+      </c>
+      <c r="X180" s="22" t="n">
+        <v>-237.708</v>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D181" s="12" t="n">
-        <v>-285.603</v>
-      </c>
-      <c r="F181" s="12" t="n">
-        <v>-125.962</v>
-      </c>
-      <c r="H181" s="12" t="n">
-        <v>-269.828</v>
-      </c>
-      <c r="J181" s="12" t="n">
-        <v>-265.274</v>
-      </c>
-      <c r="L181" s="12" t="n">
-        <v>-382.991</v>
-      </c>
-      <c r="N181" s="12" t="n">
-        <v>-264.129</v>
-      </c>
-      <c r="Q181" s="12" t="n">
-        <v>-47.257</v>
-      </c>
-      <c r="R181" s="12" t="n">
-        <v>-33.954</v>
-      </c>
-      <c r="S181" s="12" t="n">
-        <v>-60.978</v>
-      </c>
-      <c r="T181" s="12" t="n">
-        <v>-11123.02</v>
-      </c>
-      <c r="U181" s="12" t="n">
-        <v>-433.928</v>
-      </c>
-      <c r="V181" s="12" t="n">
-        <v>-285.603</v>
-      </c>
-      <c r="W181" s="12" t="n">
-        <v>-269.828</v>
-      </c>
-      <c r="X181" s="12" t="n">
-        <v>-382.991</v>
+      <c r="A181" s="20" t="inlineStr">
+        <is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="n">
+        <v>-13.739</v>
+      </c>
+      <c r="F181" s="22" t="n">
+        <v>-1.423</v>
+      </c>
+      <c r="H181" s="22" t="n">
+        <v>-4.632</v>
+      </c>
+      <c r="J181" s="22" t="n">
+        <v>-19.884</v>
+      </c>
+      <c r="L181" s="22" t="n">
+        <v>-22.649</v>
+      </c>
+      <c r="N181" s="22" t="n">
+        <v>-5.177</v>
+      </c>
+      <c r="Q181" s="22" t="n">
+        <v>-24.73</v>
+      </c>
+      <c r="R181" s="22" t="n">
+        <v>-23.44</v>
+      </c>
+      <c r="S181" s="22" t="n">
+        <v>-1.347</v>
+      </c>
+      <c r="T181" s="22" t="n">
+        <v>-4.646</v>
+      </c>
+      <c r="U181" s="22" t="n">
+        <v>-4.375</v>
+      </c>
+      <c r="V181" s="22" t="n">
+        <v>-13.739</v>
+      </c>
+      <c r="W181" s="22" t="n">
+        <v>-4.632</v>
+      </c>
+      <c r="X181" s="22" t="n">
+        <v>-22.649</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
-        </is>
-      </c>
-      <c r="J182" s="22" t="n">
+          <t>고정자산 매각</t>
+        </is>
+      </c>
+      <c r="Q182" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="N182" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="S182" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" s="22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="U182" s="22" t="n">
-        <v>0</v>
+      <c r="R182" s="22" t="n">
+        <v>0.131</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>임차보증금·보증금 회수</t>
         </is>
       </c>
       <c r="D183" s="22" t="n">
-        <v>-325.437</v>
+        <v>1.708</v>
       </c>
       <c r="F183" s="22" t="n">
-        <v>-200.5</v>
+        <v>19.052</v>
       </c>
       <c r="H183" s="22" t="n">
-        <v>-425.687</v>
+        <v>25.204</v>
       </c>
       <c r="J183" s="22" t="n">
-        <v>-249.875</v>
+        <v>0</v>
       </c>
       <c r="L183" s="22" t="n">
-        <v>-499.75</v>
+        <v>10.056</v>
       </c>
       <c r="N183" s="22" t="n">
-        <v>-2407.145</v>
-      </c>
-      <c r="Q183" s="22" t="n">
-        <v>-16.668</v>
-      </c>
-      <c r="R183" s="22" t="n">
-        <v>-16.668</v>
+        <v>3.319</v>
       </c>
       <c r="S183" s="22" t="n">
-        <v>-11.108</v>
+        <v>0</v>
       </c>
       <c r="T183" s="22" t="n">
-        <v>-75.062</v>
+        <v>3.347</v>
       </c>
       <c r="U183" s="22" t="n">
-        <v>-490.25</v>
+        <v>6.142</v>
       </c>
       <c r="V183" s="22" t="n">
-        <v>-325.437</v>
+        <v>1.708</v>
       </c>
       <c r="W183" s="22" t="n">
-        <v>-425.687</v>
+        <v>25.204</v>
       </c>
       <c r="X183" s="22" t="n">
-        <v>-499.75</v>
+        <v>10.056</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="20" t="inlineStr">
         <is>
-          <t>상장비용 지출</t>
-        </is>
-      </c>
-      <c r="Q184" s="22" t="n">
+          <t>장기투자 지출</t>
+        </is>
+      </c>
+      <c r="S184" s="22" t="n">
+        <v>-32.468</v>
+      </c>
+      <c r="T184" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="R184" s="22" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
+          <t>연결범위 변경 자회사 주식 취득</t>
         </is>
       </c>
       <c r="D185" s="22" t="n">
-        <v>35.148</v>
-      </c>
-      <c r="F185" s="22" t="n">
-        <v>12.134</v>
-      </c>
-      <c r="H185" s="22" t="n">
-        <v>14.655</v>
-      </c>
-      <c r="J185" s="22" t="n">
-        <v>7.866</v>
-      </c>
-      <c r="L185" s="22" t="n">
-        <v>8.616</v>
-      </c>
-      <c r="N185" s="22" t="n">
-        <v>3.094</v>
+        <v>0</v>
       </c>
       <c r="S185" s="22" t="n">
-        <v>717.1130000000001</v>
+        <v>0</v>
       </c>
       <c r="T185" s="22" t="n">
-        <v>8915.557000000001</v>
+        <v>-11042.562</v>
       </c>
       <c r="U185" s="22" t="n">
-        <v>21.493</v>
+        <v>-197.837</v>
       </c>
       <c r="V185" s="22" t="n">
-        <v>35.148</v>
-      </c>
-      <c r="W185" s="22" t="n">
-        <v>14.655</v>
-      </c>
-      <c r="X185" s="22" t="n">
-        <v>8.616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 발행</t>
-        </is>
-      </c>
-      <c r="D186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F186" s="22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H186" s="22" t="n">
-        <v>0.46</v>
+          <t>대여</t>
+        </is>
       </c>
       <c r="J186" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" s="22" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="S186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" s="22" t="n">
-        <v>65.94499999999999</v>
-      </c>
-      <c r="U186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V186" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W186" s="22" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="X186" s="22" t="n">
-        <v>0</v>
+      <c r="N186" s="22" t="n">
+        <v>-95</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="20" t="inlineStr">
-        <is>
-          <t>자기 신주예약권 소각</t>
-        </is>
-      </c>
-      <c r="Q187" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R187" s="22" t="n">
-        <v>-4.067</v>
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D187" s="12" t="n">
+        <v>-285.603</v>
+      </c>
+      <c r="F187" s="12" t="n">
+        <v>-125.962</v>
+      </c>
+      <c r="H187" s="12" t="n">
+        <v>-269.828</v>
+      </c>
+      <c r="J187" s="12" t="n">
+        <v>-265.274</v>
+      </c>
+      <c r="L187" s="12" t="n">
+        <v>-382.991</v>
+      </c>
+      <c r="N187" s="12" t="n">
+        <v>-264.129</v>
+      </c>
+      <c r="Q187" s="12" t="n">
+        <v>-47.257</v>
+      </c>
+      <c r="R187" s="12" t="n">
+        <v>-33.954</v>
+      </c>
+      <c r="S187" s="12" t="n">
+        <v>-60.978</v>
+      </c>
+      <c r="T187" s="12" t="n">
+        <v>-11123.02</v>
+      </c>
+      <c r="U187" s="12" t="n">
+        <v>-433.928</v>
+      </c>
+      <c r="V187" s="12" t="n">
+        <v>-285.603</v>
+      </c>
+      <c r="W187" s="12" t="n">
+        <v>-269.828</v>
+      </c>
+      <c r="X187" s="12" t="n">
+        <v>-382.991</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
-        </is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="J188" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" s="22" t="n">
+        <v>2000</v>
       </c>
       <c r="S188" s="22" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="T188" s="22" t="n">
-        <v>-0.097</v>
+        <v>4000</v>
       </c>
       <c r="U188" s="22" t="n">
         <v>0</v>
@@ -10154,220 +10377,400 @@
     <row r="189">
       <c r="A189" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
-        </is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="n">
+        <v>-325.437</v>
+      </c>
+      <c r="F189" s="22" t="n">
+        <v>-200.5</v>
+      </c>
+      <c r="H189" s="22" t="n">
+        <v>-425.687</v>
+      </c>
+      <c r="J189" s="22" t="n">
+        <v>-249.875</v>
+      </c>
+      <c r="L189" s="22" t="n">
+        <v>-499.75</v>
+      </c>
+      <c r="N189" s="22" t="n">
+        <v>-2407.145</v>
+      </c>
+      <c r="Q189" s="22" t="n">
+        <v>-16.668</v>
+      </c>
+      <c r="R189" s="22" t="n">
+        <v>-16.668</v>
       </c>
       <c r="S189" s="22" t="n">
-        <v>-1.983</v>
+        <v>-11.108</v>
       </c>
       <c r="T189" s="22" t="n">
-        <v>0</v>
+        <v>-75.062</v>
+      </c>
+      <c r="U189" s="22" t="n">
+        <v>-490.25</v>
+      </c>
+      <c r="V189" s="22" t="n">
+        <v>-325.437</v>
+      </c>
+      <c r="W189" s="22" t="n">
+        <v>-425.687</v>
+      </c>
+      <c r="X189" s="22" t="n">
+        <v>-499.75</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="20" t="inlineStr">
         <is>
-          <t>자금조달비용 지출</t>
-        </is>
-      </c>
-      <c r="S190" s="22" t="n">
+          <t>상장비용 지출</t>
+        </is>
+      </c>
+      <c r="Q190" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T190" s="22" t="n">
-        <v>-261.681</v>
+      <c r="R190" s="22" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="20" t="inlineStr">
         <is>
-          <t>자금조달비용 지출</t>
-        </is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="n">
+        <v>35.148</v>
+      </c>
+      <c r="F191" s="22" t="n">
+        <v>12.134</v>
+      </c>
+      <c r="H191" s="22" t="n">
+        <v>14.655</v>
+      </c>
+      <c r="J191" s="22" t="n">
+        <v>7.866</v>
+      </c>
+      <c r="L191" s="22" t="n">
+        <v>8.616</v>
+      </c>
+      <c r="N191" s="22" t="n">
+        <v>3.094</v>
+      </c>
+      <c r="S191" s="22" t="n">
+        <v>717.1130000000001</v>
       </c>
       <c r="T191" s="22" t="n">
-        <v>-261.681</v>
+        <v>8915.557000000001</v>
       </c>
       <c r="U191" s="22" t="n">
-        <v>0</v>
+        <v>21.493</v>
+      </c>
+      <c r="V191" s="22" t="n">
+        <v>35.148</v>
+      </c>
+      <c r="W191" s="22" t="n">
+        <v>14.655</v>
+      </c>
+      <c r="X191" s="22" t="n">
+        <v>8.616</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="20" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>신주예약권 발행</t>
         </is>
       </c>
       <c r="D192" s="22" t="n">
         <v>0</v>
       </c>
       <c r="F192" s="22" t="n">
-        <v>-10.964</v>
+        <v>0.46</v>
       </c>
       <c r="H192" s="22" t="n">
-        <v>-25.425</v>
+        <v>0.46</v>
       </c>
       <c r="J192" s="22" t="n">
-        <v>-14.129</v>
+        <v>0</v>
       </c>
       <c r="L192" s="22" t="n">
-        <v>-28.613</v>
-      </c>
-      <c r="N192" s="22" t="n">
-        <v>-15.873</v>
+        <v>0</v>
+      </c>
+      <c r="Q192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" s="22" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="S192" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" s="22" t="n">
+        <v>65.94499999999999</v>
+      </c>
+      <c r="U192" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V192" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W192" s="22" t="n">
-        <v>-25.425</v>
+        <v>0.46</v>
       </c>
       <c r="X192" s="22" t="n">
-        <v>-28.613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D193" s="12" t="n">
-        <v>-290.288</v>
-      </c>
-      <c r="F193" s="12" t="n">
-        <v>-198.869</v>
-      </c>
-      <c r="H193" s="12" t="n">
-        <v>-435.996</v>
-      </c>
-      <c r="J193" s="12" t="n">
-        <v>-256.138</v>
-      </c>
-      <c r="L193" s="12" t="n">
-        <v>-519.747</v>
-      </c>
-      <c r="N193" s="12" t="n">
-        <v>-419.925</v>
-      </c>
-      <c r="Q193" s="12" t="n">
-        <v>-16.668</v>
-      </c>
-      <c r="R193" s="12" t="n">
-        <v>-22.106</v>
-      </c>
-      <c r="S193" s="12" t="n">
-        <v>703.842</v>
-      </c>
-      <c r="T193" s="12" t="n">
-        <v>12644.66</v>
-      </c>
-      <c r="U193" s="12" t="n">
-        <v>-468.756</v>
-      </c>
-      <c r="V193" s="12" t="n">
-        <v>-290.288</v>
-      </c>
-      <c r="W193" s="12" t="n">
-        <v>-435.996</v>
-      </c>
-      <c r="X193" s="12" t="n">
-        <v>-519.747</v>
+      <c r="A193" s="20" t="inlineStr">
+        <is>
+          <t>자기 신주예약권 소각</t>
+        </is>
+      </c>
+      <c r="Q193" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" s="22" t="n">
+        <v>-4.067</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
-        </is>
-      </c>
-      <c r="D194" s="22" t="n">
-        <v>75.285</v>
-      </c>
-      <c r="F194" s="22" t="n">
-        <v>67.94</v>
-      </c>
-      <c r="H194" s="22" t="n">
-        <v>77.227</v>
-      </c>
-      <c r="J194" s="22" t="n">
-        <v>-57.071</v>
-      </c>
-      <c r="L194" s="22" t="n">
-        <v>7.416</v>
-      </c>
-      <c r="N194" s="22" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="Q194" s="22" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="R194" s="22" t="n">
-        <v>-0.148</v>
+          <t>자기주식 취득</t>
+        </is>
       </c>
       <c r="S194" s="22" t="n">
-        <v>-2.404</v>
+        <v>-0.18</v>
       </c>
       <c r="T194" s="22" t="n">
-        <v>13.542</v>
+        <v>-0.097</v>
       </c>
       <c r="U194" s="22" t="n">
-        <v>135.616</v>
-      </c>
-      <c r="V194" s="22" t="n">
-        <v>75.285</v>
-      </c>
-      <c r="W194" s="22" t="n">
-        <v>77.227</v>
-      </c>
-      <c r="X194" s="22" t="n">
-        <v>7.416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="20" t="inlineStr">
         <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="S195" s="22" t="n">
+        <v>-1.983</v>
+      </c>
+      <c r="T195" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="20" t="inlineStr">
+        <is>
+          <t>자금조달비용 지출</t>
+        </is>
+      </c>
+      <c r="S196" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" s="22" t="n">
+        <v>-261.681</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="20" t="inlineStr">
+        <is>
+          <t>자금조달비용 지출</t>
+        </is>
+      </c>
+      <c r="T197" s="22" t="n">
+        <v>-261.681</v>
+      </c>
+      <c r="U197" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="20" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="22" t="n">
+        <v>-10.964</v>
+      </c>
+      <c r="H198" s="22" t="n">
+        <v>-25.425</v>
+      </c>
+      <c r="J198" s="22" t="n">
+        <v>-14.129</v>
+      </c>
+      <c r="L198" s="22" t="n">
+        <v>-28.613</v>
+      </c>
+      <c r="N198" s="22" t="n">
+        <v>-15.873</v>
+      </c>
+      <c r="V198" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" s="22" t="n">
+        <v>-25.425</v>
+      </c>
+      <c r="X198" s="22" t="n">
+        <v>-28.613</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D199" s="12" t="n">
+        <v>-290.288</v>
+      </c>
+      <c r="F199" s="12" t="n">
+        <v>-198.869</v>
+      </c>
+      <c r="H199" s="12" t="n">
+        <v>-435.996</v>
+      </c>
+      <c r="J199" s="12" t="n">
+        <v>-256.138</v>
+      </c>
+      <c r="L199" s="12" t="n">
+        <v>-519.747</v>
+      </c>
+      <c r="N199" s="12" t="n">
+        <v>-419.925</v>
+      </c>
+      <c r="Q199" s="12" t="n">
+        <v>-16.668</v>
+      </c>
+      <c r="R199" s="12" t="n">
+        <v>-22.106</v>
+      </c>
+      <c r="S199" s="12" t="n">
+        <v>703.842</v>
+      </c>
+      <c r="T199" s="12" t="n">
+        <v>12644.66</v>
+      </c>
+      <c r="U199" s="12" t="n">
+        <v>-468.756</v>
+      </c>
+      <c r="V199" s="12" t="n">
+        <v>-290.288</v>
+      </c>
+      <c r="W199" s="12" t="n">
+        <v>-435.996</v>
+      </c>
+      <c r="X199" s="12" t="n">
+        <v>-519.747</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="n">
+        <v>75.285</v>
+      </c>
+      <c r="F200" s="22" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="H200" s="22" t="n">
+        <v>77.227</v>
+      </c>
+      <c r="J200" s="22" t="n">
+        <v>-57.071</v>
+      </c>
+      <c r="L200" s="22" t="n">
+        <v>7.416</v>
+      </c>
+      <c r="N200" s="22" t="n">
+        <v>20.28</v>
+      </c>
+      <c r="Q200" s="22" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="R200" s="22" t="n">
+        <v>-0.148</v>
+      </c>
+      <c r="S200" s="22" t="n">
+        <v>-2.404</v>
+      </c>
+      <c r="T200" s="22" t="n">
+        <v>13.542</v>
+      </c>
+      <c r="U200" s="22" t="n">
+        <v>135.616</v>
+      </c>
+      <c r="V200" s="22" t="n">
+        <v>75.285</v>
+      </c>
+      <c r="W200" s="22" t="n">
+        <v>77.227</v>
+      </c>
+      <c r="X200" s="22" t="n">
+        <v>7.416</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="D195" s="22" t="n">
+      <c r="D201" s="22" t="n">
         <v>432.139</v>
       </c>
-      <c r="F195" s="22" t="n">
+      <c r="F201" s="22" t="n">
         <v>-119.506</v>
       </c>
-      <c r="H195" s="22" t="n">
+      <c r="H201" s="22" t="n">
         <v>299.122</v>
       </c>
-      <c r="J195" s="22" t="n">
+      <c r="J201" s="22" t="n">
         <v>-353.858</v>
       </c>
-      <c r="L195" s="22" t="n">
+      <c r="L201" s="22" t="n">
         <v>396.705</v>
       </c>
-      <c r="N195" s="22" t="n">
+      <c r="N201" s="22" t="n">
         <v>-261.416</v>
       </c>
-      <c r="Q195" s="22" t="n">
+      <c r="Q201" s="22" t="n">
         <v>-17.11</v>
       </c>
-      <c r="R195" s="22" t="n">
+      <c r="R201" s="22" t="n">
         <v>83.301</v>
       </c>
-      <c r="S195" s="22" t="n">
+      <c r="S201" s="22" t="n">
         <v>1033.575</v>
       </c>
-      <c r="T195" s="22" t="n">
+      <c r="T201" s="22" t="n">
         <v>1766.153</v>
       </c>
-      <c r="U195" s="22" t="n">
+      <c r="U201" s="22" t="n">
         <v>751.596</v>
       </c>
-      <c r="V195" s="22" t="n">
+      <c r="V201" s="22" t="n">
         <v>432.139</v>
       </c>
-      <c r="W195" s="22" t="n">
+      <c r="W201" s="22" t="n">
         <v>299.122</v>
       </c>
-      <c r="X195" s="22" t="n">
+      <c r="X201" s="22" t="n">
         <v>396.705</v>
       </c>
     </row>
@@ -10408,7 +10811,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11790,7 +12193,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11842,7 +12245,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11894,7 +12297,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11946,7 +12349,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11998,7 +12401,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -12050,7 +12453,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -12102,7 +12505,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -12112,43 +12515,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -12172,7 +12575,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -12224,7 +12627,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -12276,7 +12679,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -12328,7 +12731,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -12380,7 +12783,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -12432,7 +12835,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -12502,7 +12905,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -12554,7 +12957,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -12564,49 +12967,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -12616,49 +13019,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -12668,49 +13071,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -12720,43 +13123,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -12780,7 +13183,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12832,7 +13235,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12884,7 +13287,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12936,7 +13339,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14781,299 +15184,299 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>비자스크 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>상반기 FY27</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>gmv</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>80.23</v>
       </c>
-      <c r="C6" s="57" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>gmv YoY</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>14.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>55.63</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>매출 YoY</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>16.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>adj ebitda</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="57" t="n">
         <v>7.56</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>adj ebitda YoY</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="57" t="n">
         <v>93.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="57" t="n">
         <v>8.48</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>영업이익 YoY</t>
         </is>
       </c>
-      <c r="B13" s="56" t="n">
+      <c r="B13" s="57" t="n">
         <v>70.2</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="57" t="n">
         <v>4.89</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>순이익 YoY</t>
         </is>
       </c>
-      <c r="B15" s="56" t="n">
+      <c r="B15" s="57" t="n">
         <v>169.2</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>balance 2608</t>
         </is>
       </c>
-      <c r="B17" s="53" t="n"/>
-      <c r="C17" s="53" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C18" s="54" t="inlineStr">
+      <c r="C18" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>합계 assets</t>
         </is>
       </c>
-      <c r="B19" s="56" t="n">
+      <c r="B19" s="57" t="n">
         <v>79.38</v>
       </c>
-      <c r="C19" s="57" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>net assets</t>
         </is>
       </c>
-      <c r="B20" s="56" t="n">
+      <c r="B20" s="57" t="n">
         <v>23.15</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>fixed liab</t>
         </is>
       </c>
-      <c r="B21" s="56" t="n">
+      <c r="B21" s="57" t="n">
         <v>16.49</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="A22" s="56" t="inlineStr">
         <is>
           <t>current liab</t>
         </is>
       </c>
-      <c r="B22" s="56" t="n">
+      <c r="B22" s="57" t="n">
         <v>39.73</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>밸류에이션</t>
         </is>
       </c>
-      <c r="B24" s="53" t="n"/>
-      <c r="C24" s="53" t="n"/>
+      <c r="B24" s="54" t="n"/>
+      <c r="C24" s="54" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="54" t="inlineStr">
+      <c r="A25" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B25" s="54" t="inlineStr">
+      <c r="B25" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="C25" s="54" t="inlineStr">
+      <c r="C25" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>ttm 순이익</t>
         </is>
       </c>
-      <c r="B26" s="56" t="n">
+      <c r="B26" s="57" t="n">
         <v>11.99</v>
       </c>
-      <c r="C26" s="57" t="inlineStr">
+      <c r="C26" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>PER ttm</t>
         </is>
       </c>
-      <c r="B27" s="56" t="n">
+      <c r="B27" s="57" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="55" t="inlineStr">
+      <c r="A28" s="56" t="inlineStr">
         <is>
           <t>PER 가이던스 순이익</t>
         </is>
       </c>
-      <c r="B28" s="56" t="n">
+      <c r="B28" s="57" t="n">
         <v>9.699999999999999</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>ttm 영업이익</t>
         </is>
       </c>
-      <c r="B29" s="56" t="n">
+      <c r="B29" s="57" t="n">
         <v>16.9</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="56" t="inlineStr">
         <is>
           <t>mcap to 영업이익</t>
         </is>
       </c>
-      <c r="B30" s="56" t="n">
+      <c r="B30" s="57" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -15097,24 +15500,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="58" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="59" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
